--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>execution</t>
   </si>
@@ -28,25 +28,22 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>inf</t>
-  </si>
-  <si>
-    <t>3.06 segundos</t>
-  </si>
-  <si>
-    <t>2.07 segundos</t>
-  </si>
-  <si>
-    <t>2.27 segundos</t>
-  </si>
-  <si>
-    <t>2.34 segundos</t>
-  </si>
-  <si>
-    <t>1.96 segundos</t>
+    <t>[0, 0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>2.49 segundos</t>
+  </si>
+  <si>
+    <t>2.09 segundos</t>
+  </si>
+  <si>
+    <t>1.93 segundos</t>
+  </si>
+  <si>
+    <t>2.98 segundos</t>
+  </si>
+  <si>
+    <t>2.57 segundos</t>
   </si>
 </sst>
 </file>
@@ -428,11 +425,11 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -442,11 +439,11 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
+      <c r="C3">
+        <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -456,11 +453,11 @@
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
+      <c r="C4">
+        <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -470,11 +467,11 @@
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
+      <c r="C5">
+        <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -484,11 +481,11 @@
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
-        <v>5</v>
+      <c r="C6">
+        <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>execution</t>
   </si>
@@ -31,19 +31,13 @@
     <t>[0, 0, 0, 0, 0]</t>
   </si>
   <si>
-    <t>2.49 segundos</t>
-  </si>
-  <si>
-    <t>2.09 segundos</t>
-  </si>
-  <si>
-    <t>1.93 segundos</t>
-  </si>
-  <si>
-    <t>2.98 segundos</t>
-  </si>
-  <si>
-    <t>2.57 segundos</t>
+    <t>1.77 segundos</t>
+  </si>
+  <si>
+    <t>1.13 segundos</t>
+  </si>
+  <si>
+    <t>1.23 segundos</t>
   </si>
 </sst>
 </file>
@@ -401,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -460,34 +454,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -1,69 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
-  <si>
-    <t>execution</t>
-  </si>
-  <si>
-    <t>solution_variables</t>
-  </si>
-  <si>
-    <t>best_fitness</t>
-  </si>
-  <si>
-    <t>execution_time</t>
-  </si>
-  <si>
-    <t>[0, 0, 0, 0, 0]</t>
-  </si>
-  <si>
-    <t>1.77 segundos</t>
-  </si>
-  <si>
-    <t>1.13 segundos</t>
-  </si>
-  <si>
-    <t>1.23 segundos</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -78,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -394,67 +420,127 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>execution</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>solution_variables</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>best_fitness</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>execution_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.26 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.57 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.63 segundos</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.57 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.57 segundos</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.26 segundos</t>
+          <t>1.56 segundos</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.63 segundos</t>
+          <t>0.64 segundos</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.57 segundos</t>
+          <t>0.58 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.58 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.67 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -1,37 +1,78 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+  <si>
+    <t>execution</t>
+  </si>
+  <si>
+    <t>solution_variables</t>
+  </si>
+  <si>
+    <t>best_fitness</t>
+  </si>
+  <si>
+    <t>execution_time</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>1.92 segundos</t>
+  </si>
+  <si>
+    <t>0.95 segundos</t>
+  </si>
+  <si>
+    <t>1.08 segundos</t>
+  </si>
+  <si>
+    <t>0.96 segundos</t>
+  </si>
+  <si>
+    <t>1.12 segundos</t>
+  </si>
+  <si>
+    <t>1.07 segundos</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +87,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,163 +403,123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>execution</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>solution_variables</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>best_fitness</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>execution_time</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.56 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.57 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.64 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.57 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.58 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.58 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.67 segundos</t>
-        </is>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -1,78 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
-  <si>
-    <t>execution</t>
-  </si>
-  <si>
-    <t>solution_variables</t>
-  </si>
-  <si>
-    <t>best_fitness</t>
-  </si>
-  <si>
-    <t>execution_time</t>
-  </si>
-  <si>
-    <t>[0, 0, 0, 0, 0]</t>
-  </si>
-  <si>
-    <t>1.92 segundos</t>
-  </si>
-  <si>
-    <t>0.95 segundos</t>
-  </si>
-  <si>
-    <t>1.08 segundos</t>
-  </si>
-  <si>
-    <t>0.96 segundos</t>
-  </si>
-  <si>
-    <t>1.12 segundos</t>
-  </si>
-  <si>
-    <t>1.07 segundos</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -87,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -403,123 +420,217 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>execution</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>solution_variables</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>best_fitness</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>execution_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.79 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.83 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.76 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.79 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.11 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.77 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.78 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.88 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.79 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.79 segundos</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.79 segundos</t>
+          <t>1.84 segundos</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.83 segundos</t>
+          <t>0.93 segundos</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.76 segundos</t>
+          <t>0.79 segundos</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79 segundos</t>
+          <t>0.77 segundos</t>
         </is>
       </c>
     </row>
@@ -536,97 +536,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.11 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.77 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.78 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.88 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.79 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.79 segundos</t>
+          <t>0.87 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.84 segundos</t>
+          <t>2.39 segundos</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.93 segundos</t>
+          <t>1.42 segundos</t>
         </is>
       </c>
     </row>
@@ -500,43 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.79 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.77 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.87 segundos</t>
+          <t>1.39 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.39 segundos</t>
+          <t>2.62 segundos</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.42 segundos</t>
+          <t>1.40 segundos</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.39 segundos</t>
+          <t>1.36 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.62 segundos</t>
+          <t>2.48 segundos</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.40 segundos</t>
+          <t>1.41 segundos</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.36 segundos</t>
+          <t>1.38 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.48 segundos</t>
+          <t>2.32 segundos</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.41 segundos</t>
+          <t>1.32 segundos</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.38 segundos</t>
+          <t>1.28 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>best_generations</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>execution_time</t>
         </is>
       </c>
@@ -462,9 +467,12 @@
       <c r="C2" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2.32 segundos</t>
+      <c r="D2" t="n">
+        <v>59</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.92 segundos</t>
         </is>
       </c>
     </row>
@@ -480,9 +488,12 @@
       <c r="C3" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1.32 segundos</t>
+      <c r="D3" t="n">
+        <v>59</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.28 segundos</t>
         </is>
       </c>
     </row>
@@ -498,9 +509,159 @@
       <c r="C4" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.28 segundos</t>
+      <c r="D4" t="n">
+        <v>59</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.30 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D5" t="n">
+        <v>59</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.20 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.31 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D7" t="n">
+        <v>59</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.24 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D8" t="n">
+        <v>59</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.39 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D9" t="n">
+        <v>59</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.22 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D10" t="n">
+        <v>59</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.37 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[31, 31, 31, 31, 31]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="D11" t="n">
+        <v>59</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.24 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -1,37 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+  <si>
+    <t>execution</t>
+  </si>
+  <si>
+    <t>solution_variables</t>
+  </si>
+  <si>
+    <t>best_fitness</t>
+  </si>
+  <si>
+    <t>best_generations</t>
+  </si>
+  <si>
+    <t>execution_time</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>3.61 segundos</t>
+  </si>
+  <si>
+    <t>2.18 segundos</t>
+  </si>
+  <si>
+    <t>2.69 segundos</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +81,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,252 +397,79 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>execution</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>solution_variables</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>best_fitness</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>best_generations</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>execution_time</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D2" t="n">
-        <v>59</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.92 segundos</t>
-        </is>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D3" t="n">
-        <v>59</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.28 segundos</t>
-        </is>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D4" t="n">
-        <v>59</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.30 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D5" t="n">
-        <v>59</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1.20 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D6" t="n">
-        <v>59</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.31 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D7" t="n">
-        <v>59</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1.24 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D8" t="n">
-        <v>59</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1.39 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
         <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D9" t="n">
-        <v>59</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1.22 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D10" t="n">
-        <v>59</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.37 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[31, 31, 31, 31, 31]</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="D11" t="n">
-        <v>59</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.24 segundos</t>
-        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,13 +34,13 @@
     <t>[0, 0, 0, 0, 0]</t>
   </si>
   <si>
-    <t>3.61 segundos</t>
-  </si>
-  <si>
-    <t>2.18 segundos</t>
-  </si>
-  <si>
-    <t>2.69 segundos</t>
+    <t>3.65 segundos</t>
+  </si>
+  <si>
+    <t>1.12 segundos</t>
+  </si>
+  <si>
+    <t>1.29 segundos</t>
   </si>
 </sst>
 </file>
@@ -429,7 +429,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -446,7 +446,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -463,7 +463,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -1,72 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
-  <si>
-    <t>execution</t>
-  </si>
-  <si>
-    <t>solution_variables</t>
-  </si>
-  <si>
-    <t>best_fitness</t>
-  </si>
-  <si>
-    <t>best_generations</t>
-  </si>
-  <si>
-    <t>execution_time</t>
-  </si>
-  <si>
-    <t>[0, 0, 0, 0, 0]</t>
-  </si>
-  <si>
-    <t>3.65 segundos</t>
-  </si>
-  <si>
-    <t>1.12 segundos</t>
-  </si>
-  <si>
-    <t>1.29 segundos</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -81,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -397,79 +420,252 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>execution</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>solution_variables</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>best_fitness</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>best_generations</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>execution_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.84 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.60 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>23</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.66 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.94 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4.23 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>23</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.67 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.76 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.64 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.59 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.57 segundos</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.84 segundos</t>
+          <t>1.90 segundos</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.60 segundos</t>
+          <t>0.57 segundos</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.66 segundos</t>
+          <t>0.64 segundos</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.94 segundos</t>
+          <t>0.60 segundos</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.23 segundos</t>
+          <t>0.58 segundos</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.67 segundos</t>
+          <t>0.59 segundos</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.76 segundos</t>
+          <t>0.67 segundos</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.64 segundos</t>
+          <t>0.67 segundos</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.59 segundos</t>
+          <t>0.61 segundos</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.57 segundos</t>
+          <t>0.56 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,11 +468,11 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.90 segundos</t>
+          <t>6.18 segundos</t>
         </is>
       </c>
     </row>
@@ -489,11 +489,11 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.57 segundos</t>
+          <t>0.79 segundos</t>
         </is>
       </c>
     </row>
@@ -510,11 +510,11 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.64 segundos</t>
+          <t>0.86 segundos</t>
         </is>
       </c>
     </row>
@@ -531,11 +531,11 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.60 segundos</t>
+          <t>0.67 segundos</t>
         </is>
       </c>
     </row>
@@ -552,11 +552,11 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.58 segundos</t>
+          <t>0.70 segundos</t>
         </is>
       </c>
     </row>
@@ -573,11 +573,11 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.59 segundos</t>
+          <t>0.82 segundos</t>
         </is>
       </c>
     </row>
@@ -594,11 +594,11 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.67 segundos</t>
+          <t>0.97 segundos</t>
         </is>
       </c>
     </row>
@@ -615,11 +615,11 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.67 segundos</t>
+          <t>0.74 segundos</t>
         </is>
       </c>
     </row>
@@ -636,11 +636,11 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.61 segundos</t>
+          <t>0.75 segundos</t>
         </is>
       </c>
     </row>
@@ -657,11 +657,116 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.56 segundos</t>
+          <t>0.75 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>17</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.87 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.68 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.70 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>17</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.68 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.85 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -468,11 +468,11 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.18 segundos</t>
+          <t>3.75 segundos</t>
         </is>
       </c>
     </row>
@@ -489,11 +489,11 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.79 segundos</t>
+          <t>1.95 segundos</t>
         </is>
       </c>
     </row>
@@ -510,11 +510,11 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.86 segundos</t>
+          <t>1.95 segundos</t>
         </is>
       </c>
     </row>
@@ -531,11 +531,11 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.67 segundos</t>
+          <t>2.30 segundos</t>
         </is>
       </c>
     </row>
@@ -552,11 +552,11 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.70 segundos</t>
+          <t>2.00 segundos</t>
         </is>
       </c>
     </row>
@@ -573,11 +573,11 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.82 segundos</t>
+          <t>2.05 segundos</t>
         </is>
       </c>
     </row>
@@ -594,11 +594,11 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.97 segundos</t>
+          <t>2.07 segundos</t>
         </is>
       </c>
     </row>
@@ -615,11 +615,11 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.74 segundos</t>
+          <t>2.22 segundos</t>
         </is>
       </c>
     </row>
@@ -636,11 +636,11 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.75 segundos</t>
+          <t>1.94 segundos</t>
         </is>
       </c>
     </row>
@@ -657,11 +657,11 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.75 segundos</t>
+          <t>2.04 segundos</t>
         </is>
       </c>
     </row>
@@ -678,11 +678,11 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.87 segundos</t>
+          <t>2.19 segundos</t>
         </is>
       </c>
     </row>
@@ -699,11 +699,11 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.68 segundos</t>
+          <t>2.48 segundos</t>
         </is>
       </c>
     </row>
@@ -720,11 +720,11 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.70 segundos</t>
+          <t>2.13 segundos</t>
         </is>
       </c>
     </row>
@@ -741,11 +741,11 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.68 segundos</t>
+          <t>2.34 segundos</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.85 segundos</t>
+          <t>2.14 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[25, 31, 30, 30, 31]</t>
+          <t>[30, 24, 30, 30, 24]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>467.3686443829282</v>
+        <v>310.8114961272593</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>177.82 segundos</t>
+          <t>123.79 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[30, 31, 30, 30, 31]</t>
+          <t>[30, 24, 30, 30, 24]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>391.4949618352929</v>
+        <v>310.8114961272593</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>145.24 segundos</t>
+          <t>118.15 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[30, 30, 30, 30, 31]</t>
+          <t>[30, 24, 30, 30, 24]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>375.6192482509344</v>
+        <v>310.8114961272593</v>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>143.46 segundos</t>
+          <t>120.13 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[30, 26, 30, 30, 26]</t>
+          <t>[30, 24, 30, 30, 24]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>331.9586580527748</v>
+        <v>310.8114961272593</v>
       </c>
       <c r="D5" t="n">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>127.48 segundos</t>
+          <t>119.53 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,123 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[30, 26, 30, 30, 26]</t>
+          <t>[30, 24, 30, 30, 24]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>331.9586580527748</v>
+        <v>310.8114961272593</v>
       </c>
       <c r="D6" t="n">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>108.30 segundos</t>
+          <t>131.85 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[30, 24, 30, 30, 24]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>310.8114961272593</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>127.25 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[30, 24, 30, 30, 24]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>310.8114961272593</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>171.80 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[30, 24, 30, 30, 24]</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>310.8114961272593</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>137.33 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[30, 24, 30, 30, 24]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>310.8114961272593</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>135.67 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[30, 24, 30, 30, 24]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>310.8114961272593</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>139.25 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[29, 0, 8, 8, 1]</t>
+          <t>[9, 31, 30, 9, 27]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>595.1777599285832</v>
+        <v>633.5614298340436</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>83.48 segundos</t>
+          <t>58.00 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[29, 0, 29, 29, 7]</t>
+          <t>[16, 24, 30, 16, 25]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>479.3580669982716</v>
+        <v>591.4955829101481</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>68.60 segundos</t>
+          <t>43.00 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[29, 0, 29, 29, 7]</t>
+          <t>[16, 24, 30, 16, 25]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>479.3580669982716</v>
+        <v>591.4955829101481</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.03 segundos</t>
+          <t>43.34 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[29, 0, 29, 29, 7]</t>
+          <t>[16, 24, 30, 16, 25]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>479.3580669982716</v>
+        <v>591.4955829101481</v>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>68.14 segundos</t>
+          <t>44.07 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[29, 0, 29, 29, 7]</t>
+          <t>[16, 24, 30, 16, 25]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>479.3580669982716</v>
+        <v>591.4955829101481</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69.31 segundos</t>
+          <t>42.14 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[29, 0, 29, 29, 7]</t>
+          <t>[16, 24, 30, 16, 25]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>479.3580669982716</v>
+        <v>591.4955829101481</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>68.95 segundos</t>
+          <t>41.15 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[29, 24, 29, 29, 25]</t>
+          <t>[30, 24, 30, 16, 25]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>310.8114961272589</v>
+        <v>591.3523018016016</v>
       </c>
       <c r="D8" t="n">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.38 segundos</t>
+          <t>46.66 segundos</t>
         </is>
       </c>
     </row>
@@ -608,18 +608,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[29, 24, 29, 29, 25]</t>
+          <t>[30, 24, 30, 16, 25]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>310.8114961272589</v>
+        <v>591.3523018016016</v>
       </c>
       <c r="D9" t="n">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>65.77 segundos</t>
+          <t>38.98 segundos</t>
         </is>
       </c>
     </row>
@@ -629,18 +629,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[29, 24, 29, 29, 25]</t>
+          <t>[30, 24, 30, 16, 25]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>310.8114961272589</v>
+        <v>591.3523018016016</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70.46 segundos</t>
+          <t>38.64 segundos</t>
         </is>
       </c>
     </row>
@@ -650,18 +650,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[29, 24, 29, 29, 25]</t>
+          <t>[30, 24, 30, 16, 25]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>310.8114961272589</v>
+        <v>591.3523018016016</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>72.00 segundos</t>
+          <t>39.61 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[9, 31, 30, 9, 27]</t>
+          <t>[17, 29, 11, 17, 19]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>633.5614298340436</v>
+        <v>650.082777526755</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>58.00 segundos</t>
+          <t>52.28 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[16, 24, 30, 16, 25]</t>
+          <t>[19, 25, 11, 19, 25]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>591.4955829101481</v>
+        <v>620.1639255065945</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>43.00 segundos</t>
+          <t>37.02 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[16, 24, 30, 16, 25]</t>
+          <t>[19, 25, 19, 19, 25]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>591.4955829101481</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.34 segundos</t>
+          <t>41.69 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[16, 24, 30, 16, 25]</t>
+          <t>[19, 25, 19, 19, 25]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>591.4955829101481</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44.07 segundos</t>
+          <t>39.11 segundos</t>
         </is>
       </c>
     </row>
@@ -545,123 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[16, 24, 30, 16, 25]</t>
+          <t>[19, 25, 19, 19, 25]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>591.4955829101481</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42.14 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[16, 24, 30, 16, 25]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>591.4955829101481</v>
-      </c>
-      <c r="D7" t="n">
-        <v>12</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>41.15 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[30, 24, 30, 16, 25]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>591.3523018016016</v>
-      </c>
-      <c r="D8" t="n">
-        <v>67</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>46.66 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[30, 24, 30, 16, 25]</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>591.3523018016016</v>
-      </c>
-      <c r="D9" t="n">
-        <v>67</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>38.98 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[30, 24, 30, 16, 25]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>591.3523018016016</v>
-      </c>
-      <c r="D10" t="n">
-        <v>67</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>38.64 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[30, 24, 30, 16, 25]</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>591.3523018016016</v>
-      </c>
-      <c r="D11" t="n">
-        <v>67</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>39.61 segundos</t>
+          <t>40.72 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[17, 29, 11, 17, 19]</t>
+          <t>[25, 8, 19, 19, 0]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>650.082777526755</v>
+        <v>664.3968486579445</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.28 segundos</t>
+          <t>39.24 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[19, 25, 11, 19, 25]</t>
+          <t>[10, 30, 19, 19, 31]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>620.1639255065945</v>
+        <v>621.9004747712628</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>37.02 segundos</t>
+          <t>34.12 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[19, 25, 19, 19, 25]</t>
+          <t>[10, 30, 19, 19, 31]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>454.4166296295336</v>
+        <v>621.9004747712628</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.69 segundos</t>
+          <t>34.50 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[19, 25, 19, 19, 25]</t>
+          <t>[25, 30, 27, 25, 31]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>454.4166296295336</v>
+        <v>583.326576634338</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39.11 segundos</t>
+          <t>32.87 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,123 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[19, 25, 19, 19, 25]</t>
+          <t>[25, 30, 27, 25, 31]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>454.4166296295336</v>
+        <v>583.326576634338</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.72 segundos</t>
+          <t>35.61 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[25, 30, 27, 25, 31]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>583.326576634338</v>
+      </c>
+      <c r="D7" t="n">
+        <v>37</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>34.11 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[25, 30, 27, 25, 31]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>583.326576634338</v>
+      </c>
+      <c r="D8" t="n">
+        <v>37</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>35.66 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[25, 30, 25, 25, 31]</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>331.9586580527748</v>
+      </c>
+      <c r="D9" t="n">
+        <v>74</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>34.16 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[25, 30, 25, 25, 31]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>331.9586580527748</v>
+      </c>
+      <c r="D10" t="n">
+        <v>74</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>35.90 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[25, 30, 25, 25, 31]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>331.9586580527748</v>
+      </c>
+      <c r="D11" t="n">
+        <v>74</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>35.06 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[25, 8, 19, 19, 0]</t>
+          <t>[8, 28, 15, 8, 29]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>664.3968486579445</v>
+        <v>612.2692881702279</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.24 segundos</t>
+          <t>41.84 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[10, 30, 19, 19, 31]</t>
+          <t>[8, 28, 15, 8, 29]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>621.9004747712628</v>
+        <v>612.2692881702279</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>34.12 segundos</t>
+          <t>35.28 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[10, 30, 19, 19, 31]</t>
+          <t>[8, 28, 8, 8, 29]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>621.9004747712628</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>34.50 segundos</t>
+          <t>34.78 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[25, 30, 27, 25, 31]</t>
+          <t>[8, 28, 8, 8, 29]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>583.326576634338</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32.87 segundos</t>
+          <t>33.72 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[25, 30, 27, 25, 31]</t>
+          <t>[8, 28, 8, 8, 29]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>583.326576634338</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.61 segundos</t>
+          <t>34.43 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[25, 30, 27, 25, 31]</t>
+          <t>[8, 28, 8, 8, 29]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>583.326576634338</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34.11 segundos</t>
+          <t>33.11 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[25, 30, 27, 25, 31]</t>
+          <t>[8, 28, 8, 8, 29]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>583.326576634338</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.66 segundos</t>
+          <t>32.32 segundos</t>
         </is>
       </c>
     </row>
@@ -608,18 +608,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[25, 30, 25, 25, 31]</t>
+          <t>[8, 28, 8, 8, 29]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>331.9586580527748</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34.16 segundos</t>
+          <t>33.97 segundos</t>
         </is>
       </c>
     </row>
@@ -629,18 +629,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[25, 30, 25, 25, 31]</t>
+          <t>[8, 28, 8, 8, 29]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>331.9586580527748</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35.90 segundos</t>
+          <t>33.26 segundos</t>
         </is>
       </c>
     </row>
@@ -650,18 +650,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[25, 30, 25, 25, 31]</t>
+          <t>[8, 28, 8, 8, 29]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>331.9586580527748</v>
+        <v>454.4166296295336</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.06 segundos</t>
+          <t>34.55 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[8, 28, 15, 8, 29]</t>
+          <t>[9, 0, 9, 0, 11]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>612.2692881702279</v>
+        <v>611.4937820345913</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.84 segundos</t>
+          <t>45.17 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[8, 28, 15, 8, 29]</t>
+          <t>[9, 0, 9, 9, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>612.2692881702279</v>
+        <v>454.4166296295338</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.28 segundos</t>
+          <t>32.55 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[8, 28, 8, 8, 29]</t>
+          <t>[9, 0, 9, 9, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>454.4166296295336</v>
+        <v>454.4166296295338</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>34.78 segundos</t>
+          <t>33.06 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[8, 28, 8, 8, 29]</t>
+          <t>[9, 0, 9, 9, 0]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>454.4166296295336</v>
+        <v>454.4166296295338</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.72 segundos</t>
+          <t>31.78 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[8, 28, 8, 8, 29]</t>
+          <t>[9, 0, 9, 9, 0]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>454.4166296295336</v>
+        <v>454.4166296295338</v>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34.43 segundos</t>
+          <t>31.56 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[8, 28, 8, 8, 29]</t>
+          <t>[9, 0, 9, 9, 0]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>454.4166296295336</v>
+        <v>454.4166296295338</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.11 segundos</t>
+          <t>32.57 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[8, 28, 8, 8, 29]</t>
+          <t>[9, 0, 9, 9, 0]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>454.4166296295336</v>
+        <v>454.4166296295338</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.32 segundos</t>
+          <t>32.29 segundos</t>
         </is>
       </c>
     </row>
@@ -608,18 +608,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[8, 28, 8, 8, 29]</t>
+          <t>[9, 0, 9, 9, 0]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>454.4166296295336</v>
+        <v>454.4166296295338</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.97 segundos</t>
+          <t>33.19 segundos</t>
         </is>
       </c>
     </row>
@@ -629,18 +629,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[8, 28, 8, 8, 29]</t>
+          <t>[9, 0, 9, 9, 0]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>454.4166296295336</v>
+        <v>454.4166296295338</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.26 segundos</t>
+          <t>32.59 segundos</t>
         </is>
       </c>
     </row>
@@ -650,18 +650,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[8, 28, 8, 8, 29]</t>
+          <t>[9, 0, 9, 9, 0]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>454.4166296295336</v>
+        <v>454.4166296295338</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34.55 segundos</t>
+          <t>32.82 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 0, 11]</t>
+          <t>[2, 31, 2, 2, 14]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>611.4937820345913</v>
+        <v>507.4922389713836</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45.17 segundos</t>
+          <t>39.06 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 1]</t>
+          <t>[2, 31, 2, 2, 14]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>454.4166296295338</v>
+        <v>507.4922389713836</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>32.55 segundos</t>
+          <t>33.14 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 1]</t>
+          <t>[2, 31, 2, 2, 9]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>454.4166296295338</v>
+        <v>479.358066998272</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.06 segundos</t>
+          <t>32.57 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 0]</t>
+          <t>[2, 31, 2, 2, 9]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>454.4166296295338</v>
+        <v>479.358066998272</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.78 segundos</t>
+          <t>32.99 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 0]</t>
+          <t>[2, 31, 2, 2, 9]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>454.4166296295338</v>
+        <v>479.358066998272</v>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.56 segundos</t>
+          <t>32.89 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 0]</t>
+          <t>[2, 31, 2, 2, 9]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>454.4166296295338</v>
+        <v>479.358066998272</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>32.57 segundos</t>
+          <t>32.54 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 0]</t>
+          <t>[2, 31, 2, 2, 9]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>454.4166296295338</v>
+        <v>479.358066998272</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.29 segundos</t>
+          <t>33.43 segundos</t>
         </is>
       </c>
     </row>
@@ -608,18 +608,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 0]</t>
+          <t>[2, 31, 2, 2, 9]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>454.4166296295338</v>
+        <v>479.358066998272</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.19 segundos</t>
+          <t>33.56 segundos</t>
         </is>
       </c>
     </row>
@@ -629,18 +629,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 0]</t>
+          <t>[2, 31, 2, 2, 9]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>454.4166296295338</v>
+        <v>479.358066998272</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>32.59 segundos</t>
+          <t>32.43 segundos</t>
         </is>
       </c>
     </row>
@@ -650,18 +650,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 0]</t>
+          <t>[2, 31, 2, 2, 9]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>454.4166296295338</v>
+        <v>479.358066998272</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.82 segundos</t>
+          <t>30.30 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[2, 31, 2, 2, 14]</t>
+          <t>[15, 30, 15, 8, 3]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>507.4922389713836</v>
+        <v>651.0837629184584</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.06 segundos</t>
+          <t>63.18 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[2, 31, 2, 2, 14]</t>
+          <t>[24, 2, 8, 8, 3]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>507.4922389713836</v>
+        <v>595.177759928583</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.14 segundos</t>
+          <t>36.93 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[2, 31, 2, 2, 9]</t>
+          <t>[24, 2, 8, 8, 3]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>479.358066998272</v>
+        <v>595.177759928583</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>32.57 segundos</t>
+          <t>35.39 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[2, 31, 2, 2, 9]</t>
+          <t>[24, 2, 24, 8, 3]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>479.358066998272</v>
+        <v>591.3523018016007</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32.99 segundos</t>
+          <t>37.94 segundos</t>
         </is>
       </c>
     </row>
@@ -545,123 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[2, 31, 2, 2, 9]</t>
+          <t>[24, 30, 29, 24, 24]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>479.358066998272</v>
+        <v>418.0916080723559</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32.89 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[2, 31, 2, 2, 9]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>479.358066998272</v>
-      </c>
-      <c r="D7" t="n">
-        <v>27</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>32.54 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[2, 31, 2, 2, 9]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>479.358066998272</v>
-      </c>
-      <c r="D8" t="n">
-        <v>27</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>33.43 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[2, 31, 2, 2, 9]</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>479.358066998272</v>
-      </c>
-      <c r="D9" t="n">
-        <v>27</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>33.56 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[2, 31, 2, 2, 9]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>479.358066998272</v>
-      </c>
-      <c r="D10" t="n">
-        <v>27</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>32.43 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[2, 31, 2, 2, 9]</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>479.358066998272</v>
-      </c>
-      <c r="D11" t="n">
-        <v>27</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>30.30 segundos</t>
+          <t>35.35 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[15, 30, 15, 8, 3]</t>
+          <t>[0, 18, 31, 31, 11]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>651.0837629184584</v>
+        <v>740.0044014922461</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>63.18 segundos</t>
+          <t>26.29 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[24, 2, 8, 8, 3]</t>
+          <t>[0, 18, 31, 31, 11]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>595.177759928583</v>
+        <v>740.0044014922461</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36.93 segundos</t>
+          <t>13.95 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[24, 2, 8, 8, 3]</t>
+          <t>[5, 18, 31, 31, 25]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>595.177759928583</v>
+        <v>710.8915228071769</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35.39 segundos</t>
+          <t>11.85 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[24, 2, 24, 8, 3]</t>
+          <t>[11, 10, 28, 28, 11]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>591.3523018016007</v>
+        <v>662.590696010637</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.94 segundos</t>
+          <t>12.07 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,60 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[24, 30, 29, 24, 24]</t>
+          <t>[11, 10, 28, 28, 11]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>418.0916080723559</v>
+        <v>662.590696010637</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.35 segundos</t>
+          <t>12.99 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[11, 10, 28, 28, 11]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>662.590696010637</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>13.90 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[11, 10, 28, 28, 11]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>662.590696010637</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>14.26 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[0, 18, 31, 31, 11]</t>
+          <t>[9, 15, 9, 3, 10]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>740.0044014922461</v>
+        <v>822.8622746269281</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.29 segundos</t>
+          <t>17.77 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[0, 18, 31, 31, 11]</t>
+          <t>[9, 15, 9, 3, 27]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>740.0044014922461</v>
+        <v>708.4128124719655</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13.95 segundos</t>
+          <t>11.54 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[5, 18, 31, 31, 25]</t>
+          <t>[9, 15, 9, 3, 27]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>710.8915228071769</v>
+        <v>708.4128124719655</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.85 segundos</t>
+          <t>9.68 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[11, 10, 28, 28, 11]</t>
+          <t>[9, 3, 9, 3, 5]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>662.590696010637</v>
+        <v>641.4035993230735</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.07 segundos</t>
+          <t>9.59 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[11, 10, 28, 28, 11]</t>
+          <t>[9, 3, 9, 24, 30]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>662.590696010637</v>
+        <v>620.4816894634546</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.99 segundos</t>
+          <t>10.71 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[11, 10, 28, 28, 11]</t>
+          <t>[9, 3, 9, 24, 30]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>662.590696010637</v>
+        <v>620.4816894634546</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.90 segundos</t>
+          <t>11.56 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,291 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[11, 10, 28, 28, 11]</t>
+          <t>[9, 3, 9, 24, 30]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>662.590696010637</v>
+        <v>620.4816894634546</v>
       </c>
       <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8.80 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 11]</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>605.8890668516806</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9.13 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 11]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>605.8890668516806</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7.88 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 11]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>605.8890668516806</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9.01 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 11]</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>605.8890668516806</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8.22 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 11]</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>605.8890668516806</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7.54 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>14.26 segundos</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 11]</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>605.8890668516806</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7.26 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 11]</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>605.8890668516806</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>7.06 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 11]</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>605.8890668516806</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8.71 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 11]</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>605.8890668516806</v>
+      </c>
+      <c r="D17" t="n">
+        <v>30</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>7.67 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 4]</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>583.6386771855562</v>
+      </c>
+      <c r="D18" t="n">
+        <v>65</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8.67 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 4]</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>583.6386771855562</v>
+      </c>
+      <c r="D19" t="n">
+        <v>65</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8.35 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 4]</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>583.6386771855562</v>
+      </c>
+      <c r="D20" t="n">
+        <v>65</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>7.58 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[9, 3, 9, 31, 4]</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>583.6386771855562</v>
+      </c>
+      <c r="D21" t="n">
+        <v>65</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8.91 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[9, 15, 9, 3, 10]</t>
+          <t>[24, 27, 19, 26, 2]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>822.8622746269281</v>
+        <v>973.1422387959925</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.77 segundos</t>
+          <t>22.29 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[9, 15, 9, 3, 27]</t>
+          <t>[9, 28, 9, 7, 19]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>708.4128124719655</v>
+        <v>779.0647539103967</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.54 segundos</t>
+          <t>14.35 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[9, 15, 9, 3, 27]</t>
+          <t>[9, 28, 9, 6, 28]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>708.4128124719655</v>
+        <v>748.5297964049162</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.68 segundos</t>
+          <t>14.95 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[9, 3, 9, 3, 5]</t>
+          <t>[9, 28, 9, 6, 28]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>641.4035993230735</v>
+        <v>748.5297964049162</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.59 segundos</t>
+          <t>14.11 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[9, 3, 9, 24, 30]</t>
+          <t>[9, 28, 9, 6, 28]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>620.4816894634546</v>
+        <v>748.5297964049162</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.71 segundos</t>
+          <t>11.57 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[9, 3, 9, 24, 30]</t>
+          <t>[9, 28, 9, 6, 28]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>620.4816894634546</v>
+        <v>748.5297964049162</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.56 segundos</t>
+          <t>14.30 segundos</t>
         </is>
       </c>
     </row>
@@ -587,291 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[9, 3, 9, 24, 30]</t>
+          <t>[9, 28, 9, 6, 28]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>620.4816894634546</v>
+        <v>748.5297964049162</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8.80 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 11]</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>605.8890668516806</v>
-      </c>
-      <c r="D9" t="n">
-        <v>30</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>9.13 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 11]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>605.8890668516806</v>
-      </c>
-      <c r="D10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>7.88 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 11]</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>605.8890668516806</v>
-      </c>
-      <c r="D11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>9.01 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 11]</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>605.8890668516806</v>
-      </c>
-      <c r="D12" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>8.22 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 11]</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>605.8890668516806</v>
-      </c>
-      <c r="D13" t="n">
-        <v>30</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>7.54 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 11]</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>605.8890668516806</v>
-      </c>
-      <c r="D14" t="n">
-        <v>30</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>7.26 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 11]</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>605.8890668516806</v>
-      </c>
-      <c r="D15" t="n">
-        <v>30</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>7.06 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 11]</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>605.8890668516806</v>
-      </c>
-      <c r="D16" t="n">
-        <v>30</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>8.71 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 11]</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>605.8890668516806</v>
-      </c>
-      <c r="D17" t="n">
-        <v>30</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>7.67 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 4]</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>583.6386771855562</v>
-      </c>
-      <c r="D18" t="n">
-        <v>65</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>8.67 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 4]</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>583.6386771855562</v>
-      </c>
-      <c r="D19" t="n">
-        <v>65</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>8.35 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 4]</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>583.6386771855562</v>
-      </c>
-      <c r="D20" t="n">
-        <v>65</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>7.58 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>[9, 3, 9, 31, 4]</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>583.6386771855562</v>
-      </c>
-      <c r="D21" t="n">
-        <v>65</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>8.91 segundos</t>
+          <t>11.40 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[27, 1, 15, 1, 7]</t>
+          <t>[7, 23, 25, 25, 3]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>797.1688594793779</v>
+        <v>918.6437425091643</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.53 segundos</t>
+          <t>17.71 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[28, 24, 24, 25, 28]</t>
+          <t>[7, 0, 14, 25, 3]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>779.6795632580754</v>
+        <v>896.2855616073953</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.84 segundos</t>
+          <t>9.38 segundos</t>
         </is>
       </c>
     </row>
@@ -503,144 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[28, 24, 24, 25, 28]</t>
+          <t>[13, 30, 1, 1, 21]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>779.6795632580754</v>
+        <v>782.3592118449277</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>29.19 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[6, 26, 24, 18, 26]</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>761.3594327875034</v>
-      </c>
-      <c r="D5" t="n">
-        <v>13</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>15.35 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[6, 26, 24, 25, 26]</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>752.5702859361352</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>16.84 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[6, 26, 6, 28, 26]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>714.8327519091707</v>
-      </c>
-      <c r="D7" t="n">
-        <v>22</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>21.28 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[6, 26, 6, 25, 26]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>607.7211707558531</v>
-      </c>
-      <c r="D8" t="n">
-        <v>27</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>13.56 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[6, 26, 6, 25, 26]</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>607.7211707558531</v>
-      </c>
-      <c r="D9" t="n">
-        <v>27</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>14.87 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[6, 26, 6, 25, 26]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>607.7211707558531</v>
-      </c>
-      <c r="D10" t="n">
-        <v>27</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>13.94 segundos</t>
+          <t>13.30 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[7, 23, 25, 25, 3]</t>
+          <t>[12, 24, 12, 17, 30]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>918.6437425091643</v>
+        <v>786.7753405517559</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.71 segundos</t>
+          <t>12.75 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[7, 0, 14, 25, 3]</t>
+          <t>[12, 24, 12, 3, 30]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>896.2855616073953</v>
+        <v>651.0837629184583</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.38 segundos</t>
+          <t>6.77 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,81 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[13, 30, 1, 1, 21]</t>
+          <t>[12, 24, 12, 3, 30]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>782.3592118449277</v>
+        <v>651.0837629184583</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.30 segundos</t>
+          <t>6.49 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[12, 24, 12, 3, 30]</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>651.0837629184583</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7.13 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[3, 24, 13, 3, 30]</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>649.1123004481256</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5.07 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[3, 24, 29, 29, 14]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>649.0284214777098</v>
+      </c>
+      <c r="D7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5.03 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[12, 24, 12, 17, 30]</t>
+          <t>[24, 25, 9, 17, 26]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>786.7753405517559</v>
+        <v>781.1347042216174</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.75 segundos</t>
+          <t>12.99 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[12, 24, 12, 3, 30]</t>
+          <t>[24, 25, 17, 17, 26]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>651.0837629184583</v>
+        <v>612.9360520340507</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.77 segundos</t>
+          <t>6.12 segundos</t>
         </is>
       </c>
     </row>
@@ -503,81 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[12, 24, 12, 3, 30]</t>
+          <t>[24, 26, 17, 17, 26]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>651.0837629184583</v>
+        <v>600.9683944239088</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.49 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[12, 24, 12, 3, 30]</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>651.0837629184583</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>7.13 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[3, 24, 13, 3, 30]</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>649.1123004481256</v>
-      </c>
-      <c r="D6" t="n">
-        <v>18</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>5.07 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[3, 24, 29, 29, 14]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>649.0284214777098</v>
-      </c>
-      <c r="D7" t="n">
-        <v>22</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>5.03 segundos</t>
+          <t>5.82 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[24, 25, 9, 17, 26]</t>
+          <t>[1, 26, 1, 26, 3]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>781.1347042216174</v>
+        <v>585.4287983302329</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.99 segundos</t>
+          <t>12.08 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[24, 25, 17, 17, 26]</t>
+          <t>[1, 26, 1, 26, 3]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>612.9360520340507</v>
+        <v>585.4287983302329</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.12 segundos</t>
+          <t>6.52 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[24, 26, 17, 17, 26]</t>
+          <t>[1, 26, 1, 26, 3]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>600.9683944239088</v>
+        <v>585.4287983302329</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.82 segundos</t>
+          <t>5.75 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[1, 26, 1, 26, 3]</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>585.4287983302329</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6.05 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 26, 1, 26, 3]</t>
+          <t>[16, 8, 31, 24, 2]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>585.4287983302329</v>
+        <v>793.8571143949455</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.08 segundos</t>
+          <t>11.88 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 26, 1, 26, 3]</t>
+          <t>[10, 25, 31, 31, 4]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>585.4287983302329</v>
+        <v>649.0591281073408</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.52 segundos</t>
+          <t>6.18 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 26, 1, 26, 3]</t>
+          <t>[10, 25, 31, 31, 4]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>585.4287983302329</v>
+        <v>649.0591281073408</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.75 segundos</t>
+          <t>6.26 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 26, 1, 26, 3]</t>
+          <t>[10, 25, 31, 31, 4]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>585.4287983302329</v>
+        <v>649.0591281073408</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.05 segundos</t>
+          <t>5.59 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[10, 25, 31, 31, 12]</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>605.4002632829288</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5.99 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[16, 8, 31, 24, 2]</t>
+          <t>[0, 7, 29, 13, 19]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>793.8571143949455</v>
+        <v>826.8186450627086</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.88 segundos</t>
+          <t>26.87 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[10, 25, 31, 31, 4]</t>
+          <t>[10, 30, 0, 6, 12]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>649.0591281073408</v>
+        <v>781.9204880243485</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.18 segundos</t>
+          <t>12.05 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[10, 25, 31, 31, 4]</t>
+          <t>[12, 30, 0, 6, 12]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>649.0591281073408</v>
+        <v>778.6603908102493</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.26 segundos</t>
+          <t>10.18 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[10, 25, 31, 31, 4]</t>
+          <t>[6, 24, 24, 16, 8]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>649.0591281073408</v>
+        <v>760.3643409276167</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.59 segundos</t>
+          <t>14.29 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,60 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[10, 25, 31, 31, 12]</t>
+          <t>[6, 24, 24, 16, 8]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>605.4002632829288</v>
+        <v>760.3643409276167</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.99 segundos</t>
+          <t>13.44 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[6, 24, 24, 16, 8]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>760.3643409276167</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>11.93 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[6, 24, 24, 24, 8]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>584.4893374254052</v>
+      </c>
+      <c r="D8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8.94 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[0, 7, 29, 13, 19]</t>
+          <t>[26, 18, 10, 16, 16]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>826.8186450627086</v>
+        <v>1030.876938686809</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.87 segundos</t>
+          <t>13.43 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[10, 30, 0, 6, 12]</t>
+          <t>[21, 10, 4, 4, 23]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>781.9204880243485</v>
+        <v>513.2684085326746</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.05 segundos</t>
+          <t>9.48 segundos</t>
         </is>
       </c>
     </row>
@@ -503,102 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[12, 30, 0, 6, 12]</t>
+          <t>[21, 10, 4, 4, 23]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>778.6603908102493</v>
+        <v>513.2684085326746</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10.18 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[6, 24, 24, 16, 8]</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>760.3643409276167</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>14.29 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[6, 24, 24, 16, 8]</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>760.3643409276167</v>
-      </c>
-      <c r="D6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>13.44 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[6, 24, 24, 16, 8]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>760.3643409276167</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>11.93 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[6, 24, 24, 24, 8]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>584.4893374254052</v>
-      </c>
-      <c r="D8" t="n">
-        <v>26</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>8.94 segundos</t>
+          <t>8.68 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[26, 18, 10, 16, 16]</t>
+          <t>[30, 23, 13, 13, 19]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1030.876938686809</v>
+        <v>846.5817703871533</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.43 segundos</t>
+          <t>19.89 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[21, 10, 4, 4, 23]</t>
+          <t>[26, 6, 13, 13, 19]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>513.2684085326746</v>
+        <v>685.3911869160343</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.48 segundos</t>
+          <t>10.89 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,2979 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[21, 10, 4, 4, 23]</t>
+          <t>[31, 24, 13, 13, 6]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>513.2684085326746</v>
+        <v>661.1336508915502</v>
       </c>
       <c r="D4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>11.35 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[29, 0, 1, 3, 5]</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>847.0797876815009</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>16.33 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[29, 0, 4, 3, 5]</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>834.4044445565989</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11.59 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[30, 0, 24, 3, 5]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>737.9923633768288</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>11.93 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[5, 28, 31, 11, 5]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>888.1950246486809</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15.13 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[5, 28, 28, 11, 5]</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>788.8759804695253</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>11.68 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[5, 28, 28, 3, 5]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>756.3531452348894</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12.31 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[18, 26, 18, 25, 25]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>610.5220226302893</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15.81 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[18, 26, 18, 25, 25]</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>610.5220226302893</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>11.38 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[18, 25, 18, 25, 25]</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>607.7211707558515</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>11.04 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[29, 29, 19, 13, 27]</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>944.6459271678667</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>16.23 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[29, 29, 19, 13, 8]</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>860.8565902042925</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>12.52 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[3, 29, 19, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>801.4108200185689</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>11.89 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[16, 7, 16, 29, 31]</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>656.1490671292927</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>15.34 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[16, 7, 16, 29, 24]</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>652.8577659149166</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>13.76 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>[16, 7, 16, 29, 24]</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>652.8577659149166</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>12.20 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[16, 26, 25, 31, 3]</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>792.8298963468076</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>17.28 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[16, 9, 31, 31, 3]</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>652.3223258737335</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>14.21 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>[16, 9, 31, 31, 3]</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>652.3223258737335</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>11.98 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>[1, 13, 5, 18, 7]</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>792.8554795598354</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>15.92 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>[10, 11, 4, 10, 17]</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>738.4196843003388</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>13.53 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[10, 11, 25, 10, 17]</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>709.7513417038922</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>11.47 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>[24, 28, 17, 24, 26]</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>702.4583052636711</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>16.51 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>[24, 3, 17, 24, 26]</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>617.1380590752259</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>12.45 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>[24, 30, 17, 24, 26]</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>584.7619826237641</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>11.88 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[6, 26, 0, 12, 26]</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>761.430784362382</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>16.42 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>[6, 26, 0, 12, 26]</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>761.430784362382</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>11.75 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[6, 26, 0, 12, 26]</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>761.430784362382</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>12.22 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>[30, 25, 8, 30, 31]</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>717.3134203970682</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>15.73 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>[30, 25, 10, 30, 19]</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>650.8517697883511</v>
+      </c>
+      <c r="D33" t="n">
         <v>7</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>8.68 segundos</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>12.36 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>[30, 25, 10, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>613.0800854248301</v>
+      </c>
+      <c r="D34" t="n">
+        <v>11</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>10.99 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>[31, 16, 25, 31, 17]</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>695.5127233955105</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>16.03 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>[31, 1, 9, 31, 17]</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>650.8517697883511</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>12.49 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>[31, 1, 9, 31, 1]</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>583.951185369161</v>
+      </c>
+      <c r="D37" t="n">
+        <v>13</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>12.07 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>[12, 2, 25, 12, 2]</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>623.8716593616098</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>15.90 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>[12, 2, 25, 12, 2]</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>623.8716593616098</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>12.58 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>[12, 2, 25, 12, 2]</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>623.8716593616098</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>11.32 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>[13, 7, 13, 31, 24]</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>652.8577659149166</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>16.43 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>[13, 7, 13, 31, 24]</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>652.8577659149166</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>12.78 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>[13, 7, 13, 31, 24]</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>652.8577659149166</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>12.08 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>[24, 0, 8, 24, 10]</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>652.4352342173285</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>17.39 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>[24, 30, 8, 24, 17]</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>650.851769788351</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>13.41 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>[24, 30, 8, 24, 26]</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>584.7619826237641</v>
+      </c>
+      <c r="D46" t="n">
+        <v>13</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10.97 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>[29, 25, 29, 9, 25]</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>607.7961274850295</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>16.25 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>[29, 25, 29, 9, 25]</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>607.7961274850295</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>10.48 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>[29, 25, 29, 9, 25]</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>607.7961274850295</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>11.57 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>[0, 4, 18, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>628.0273227550213</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>13.97 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>[0, 4, 18, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>628.0273227550213</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>12.22 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>[0, 31, 18, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>613.08008542483</v>
+      </c>
+      <c r="D52" t="n">
+        <v>12</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>11.92 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>[3, 30, 3, 6, 24]</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>732.5761848742844</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>16.08 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>[6, 0, 29, 6, 0]</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>591.4955829101477</v>
+      </c>
+      <c r="D54" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>12.67 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>[6, 0, 29, 6, 0]</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>591.4955829101477</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>12.24 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>[24, 2, 24, 9, 24]</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>589.2140070307033</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>16.13 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>[24, 2, 24, 9, 24]</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>589.2140070307033</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>11.48 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>[24, 2, 24, 9, 24]</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>589.2140070307033</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>11.22 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>[5, 0, 0, 24, 5]</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>685.4152695425225</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>15.94 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>[24, 0, 0, 24, 5]</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>627.4062618379006</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>11.41 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>[24, 0, 3, 24, 5]</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>582.3490195021119</v>
+      </c>
+      <c r="D61" t="n">
+        <v>11</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>12.17 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>[24, 25, 10, 31, 19]</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>804.4764953628312</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>15.95 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>[24, 25, 10, 31, 19]</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>804.4764953628312</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>11.88 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>[7, 27, 7, 3, 16]</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>750.9305819372843</v>
+      </c>
+      <c r="D64" t="n">
+        <v>11</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>11.78 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>[23, 29, 23, 13, 15]</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>796.4604731412492</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>17.20 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>[23, 29, 23, 13, 15]</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>796.4604731412492</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>10.34 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>[29, 0, 14, 29, 5]</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>649.9070763321289</v>
+      </c>
+      <c r="D67" t="n">
+        <v>12</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>11.19 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>[4, 4, 13, 24, 26]</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>804.4329392785953</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>15.36 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>[4, 28, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>584.7875991409136</v>
+      </c>
+      <c r="D69" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>11.10 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>[4, 28, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>584.7875991409136</v>
+      </c>
+      <c r="D70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>10.31 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>[11, 3, 2, 18, 2]</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>792.9751831361273</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>14.90 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>[11, 3, 2, 29, 2]</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>756.1824244393304</v>
+      </c>
+      <c r="D72" t="n">
+        <v>7</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>9.65 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>[11, 3, 2, 29, 2]</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>756.1824244393304</v>
+      </c>
+      <c r="D73" t="n">
+        <v>7</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>11.86 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>[15, 21, 15, 15, 28]</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>684.8263018300131</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>15.85 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>[17, 0, 17, 10, 0]</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>646.6168270920224</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>12.88 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>[17, 0, 17, 10, 0]</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>646.6168270920224</v>
+      </c>
+      <c r="D76" t="n">
+        <v>8</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>10.02 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>[5, 27, 19, 19, 28]</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>621.9004747712621</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>14.03 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>[5, 27, 19, 19, 28]</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>621.9004747712621</v>
+      </c>
+      <c r="D78" t="n">
+        <v>4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>11.63 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>3</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>[5, 27, 19, 19, 28]</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>621.9004747712621</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>11.06 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>[31, 5, 31, 14, 28]</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>791.6096606177399</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>15.49 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>[31, 5, 31, 31, 28]</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>679.9681387570566</v>
+      </c>
+      <c r="D81" t="n">
+        <v>8</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>12.10 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>3</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>[31, 24, 31, 31, 11]</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>479.3580669982718</v>
+      </c>
+      <c r="D82" t="n">
+        <v>12</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>12.15 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>[20, 26, 20, 31, 20]</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>579.8240831473222</v>
+      </c>
+      <c r="D83" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>16.75 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>[20, 26, 20, 31, 20]</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>579.8240831473222</v>
+      </c>
+      <c r="D84" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>12.39 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>[20, 26, 20, 20, 20]</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>459.4619885894684</v>
+      </c>
+      <c r="D85" t="n">
+        <v>11</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>12.83 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>[2, 13, 12, 30, 18]</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>847.8604480162528</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>17.38 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>[16, 0, 16, 7, 27]</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>651.0837629184591</v>
+      </c>
+      <c r="D87" t="n">
+        <v>9</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>12.97 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>[16, 0, 16, 7, 27]</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>651.0837629184591</v>
+      </c>
+      <c r="D88" t="n">
+        <v>9</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>11.60 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>[1, 2, 1, 20, 16]</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>817.7707929847866</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>14.98 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>[1, 2, 1, 1, 16]</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>544.5151144812581</v>
+      </c>
+      <c r="D90" t="n">
+        <v>6</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>14.40 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>[1, 2, 1, 1, 16]</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>544.5151144812581</v>
+      </c>
+      <c r="D91" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>11.90 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>[9, 13, 19, 19, 5]</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>843.7338479457957</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>16.34 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>[17, 27, 25, 25, 27]</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>603.9926747370439</v>
+      </c>
+      <c r="D93" t="n">
+        <v>6</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>11.48 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>[17, 27, 25, 25, 27]</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>603.9926747370439</v>
+      </c>
+      <c r="D94" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>10.14 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>[13, 13, 4, 4, 18]</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>836.8949843947177</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>14.89 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>[6, 28, 4, 4, 6]</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>615.8011004849803</v>
+      </c>
+      <c r="D96" t="n">
+        <v>6</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>12.43 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>[4, 28, 4, 4, 6]</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>459.4619885894684</v>
+      </c>
+      <c r="D97" t="n">
+        <v>14</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>11.50 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>[31, 10, 27, 4, 27]</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>843.1231347434178</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>15.27 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>[31, 10, 27, 18, 27]</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>790.7446230517668</v>
+      </c>
+      <c r="D99" t="n">
+        <v>9</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>12.29 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>3</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>[31, 10, 27, 18, 27]</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>790.7446230517668</v>
+      </c>
+      <c r="D100" t="n">
+        <v>9</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>13.12 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>[25, 26, 3, 9, 2]</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>929.4784903516644</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>14.62 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>[25, 10, 25, 9, 25]</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>696.3937072465774</v>
+      </c>
+      <c r="D102" t="n">
+        <v>9</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>11.99 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>3</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>[25, 29, 25, 9, 25]</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>603.9143884297888</v>
+      </c>
+      <c r="D103" t="n">
+        <v>14</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>12.61 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>[24, 9, 19, 24, 30]</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>757.5511448933073</v>
+      </c>
+      <c r="D104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>17.60 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>[24, 30, 14, 24, 30]</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>616.327261820623</v>
+      </c>
+      <c r="D105" t="n">
+        <v>8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>10.02 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>3</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>[24, 30, 14, 24, 30]</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>616.327261820623</v>
+      </c>
+      <c r="D106" t="n">
+        <v>8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>10.88 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>[31, 6, 5, 5, 11]</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>656.5280571326069</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>15.41 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>[31, 6, 5, 5, 11]</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>656.5280571326069</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>11.41 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>3</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>[31, 6, 5, 5, 11]</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>656.5280571326069</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>11.18 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>[27, 1, 4, 4, 3]</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>873.477001295767</v>
+      </c>
+      <c r="D110" t="n">
+        <v>4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>14.74 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>[22, 29, 6, 22, 22]</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>723.4106611775105</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>10.08 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>[22, 29, 22, 22, 22]</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>459.4619885894684</v>
+      </c>
+      <c r="D112" t="n">
+        <v>12</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>11.12 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>[6, 28, 2, 2, 2]</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>584.7875991409136</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>15.63 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>[6, 2, 2, 2, 2]</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>583.6375571912222</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>11.56 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>3</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>[7, 2, 2, 2, 2]</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>568.3021842508629</v>
+      </c>
+      <c r="D115" t="n">
+        <v>10</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>11.05 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>[5, 5, 14, 26, 6]</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>811.4100082011225</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>16.60 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>[27, 0, 26, 27, 17]</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>787.258477239218</v>
+      </c>
+      <c r="D117" t="n">
+        <v>7</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>12.65 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>3</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>[15, 0, 7, 25, 15]</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>776.7266599516915</v>
+      </c>
+      <c r="D118" t="n">
+        <v>11</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>10.85 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>[2, 24, 17, 2, 30]</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>649.1123004481256</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>16.35 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>[2, 24, 17, 2, 30]</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>649.1123004481256</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>12.03 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>3</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>[2, 24, 17, 2, 2]</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>613.08008542483</v>
+      </c>
+      <c r="D121" t="n">
+        <v>12</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>10.98 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>1</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>[4, 12, 30, 30, 0]</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>710.8915228071769</v>
+      </c>
+      <c r="D122" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>16.51 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>[4, 12, 30, 30, 0]</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>710.8915228071769</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>11.21 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>3</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>[15, 0, 30, 30, 0]</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>615.4793135958349</v>
+      </c>
+      <c r="D124" t="n">
+        <v>13</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>11.57 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>[10, 1, 18, 10, 1]</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>644.6453646216891</v>
+      </c>
+      <c r="D125" t="n">
+        <v>4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>14.23 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>[10, 1, 24, 10, 1]</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>623.8716593616098</v>
+      </c>
+      <c r="D126" t="n">
+        <v>9</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>11.77 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>3</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>[10, 1, 24, 10, 1]</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>623.8716593616098</v>
+      </c>
+      <c r="D127" t="n">
+        <v>9</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>10.76 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>[2, 11, 16, 30, 26]</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>821.5500569055391</v>
+      </c>
+      <c r="D128" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>14.07 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>[2, 13, 13, 30, 26]</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>817.8028758749615</v>
+      </c>
+      <c r="D129" t="n">
+        <v>6</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>9.20 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>3</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>[13, 24, 13, 30, 2]</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>649.5945681485239</v>
+      </c>
+      <c r="D130" t="n">
+        <v>14</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>11.91 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>[17, 6, 24, 17, 1]</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>660.7146716395082</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>15.65 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>[17, 28, 1, 17, 24]</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>657.0069377844931</v>
+      </c>
+      <c r="D132" t="n">
+        <v>9</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>9.04 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>3</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>[17, 28, 1, 17, 24]</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>657.0069377844931</v>
+      </c>
+      <c r="D133" t="n">
+        <v>9</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>11.22 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>[2, 6, 31, 11, 2]</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>773.4663613874823</v>
+      </c>
+      <c r="D134" t="n">
+        <v>4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>15.04 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>[2, 1, 31, 11, 2]</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>767.2214188577072</v>
+      </c>
+      <c r="D135" t="n">
+        <v>7</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>13.32 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>3</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>[2, 1, 31, 6, 2]</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>743.2866788218446</v>
+      </c>
+      <c r="D136" t="n">
+        <v>11</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>8.44 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>[8, 31, 0, 8, 6]</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>765.0006328376103</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>14.72 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>[8, 31, 0, 6, 8]</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>754.1884821618312</v>
+      </c>
+      <c r="D138" t="n">
+        <v>9</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>10.41 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>3</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>[8, 31, 0, 6, 8]</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>754.1884821618312</v>
+      </c>
+      <c r="D139" t="n">
+        <v>9</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>11.17 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>[9, 22, 9, 27, 29]</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>817.3396506004119</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>14.34 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>[9, 5, 9, 27, 29]</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>780.96395516916</v>
+      </c>
+      <c r="D141" t="n">
+        <v>5</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>11.61 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>3</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>[9, 4, 9, 27, 29]</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>623.7729906778309</v>
+      </c>
+      <c r="D142" t="n">
+        <v>10</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>11.78 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>[11, 11, 11, 8, 7]</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>876.5121300049924</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>14.51 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>[11, 11, 11, 30, 7]</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>707.4664884606975</v>
+      </c>
+      <c r="D144" t="n">
+        <v>7</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>10.72 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>3</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>[11, 11, 11, 30, 7]</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>707.4664884606975</v>
+      </c>
+      <c r="D145" t="n">
+        <v>7</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>7.86 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[30, 23, 13, 13, 19]</t>
+          <t>[7, 24, 24, 0, 26]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>846.5817703871533</v>
+        <v>729.7895087367011</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.89 segundos</t>
+          <t>16.23 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[26, 6, 13, 13, 19]</t>
+          <t>[7, 25, 25, 25, 7]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>685.3911869160343</v>
+        <v>612.3353178191887</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.89 segundos</t>
+          <t>9.28 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[31, 24, 13, 13, 6]</t>
+          <t>[25, 25, 25, 25, 7]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>661.1336508915502</v>
+        <v>500.5052289237871</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.35 segundos</t>
+          <t>11.03 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[29, 0, 1, 3, 5]</t>
+          <t>[15, 26, 4, 15, 7]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>847.0797876815009</v>
+        <v>832.2447961677849</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16.33 segundos</t>
+          <t>12.06 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[29, 0, 4, 3, 5]</t>
+          <t>[15, 26, 31, 25, 26]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>834.4044445565989</v>
+        <v>748.7205192358799</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.59 segundos</t>
+          <t>8.77 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[30, 0, 24, 3, 5]</t>
+          <t>[15, 26, 31, 25, 26]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>737.9923633768288</v>
+        <v>748.7205192358799</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.93 segundos</t>
+          <t>8.88 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[5, 28, 31, 11, 5]</t>
+          <t>[11, 0, 11, 27, 19]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>888.1950246486809</v>
+        <v>678.9257875939604</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.13 segundos</t>
+          <t>11.37 segundos</t>
         </is>
       </c>
     </row>
@@ -608,18 +608,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[5, 28, 28, 11, 5]</t>
+          <t>[15, 9, 8, 8, 15]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>788.8759804695253</v>
+        <v>671.4552831611516</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.68 segundos</t>
+          <t>10.07 segundos</t>
         </is>
       </c>
     </row>
@@ -629,18 +629,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[5, 28, 28, 3, 5]</t>
+          <t>[15, 30, 8, 8, 15]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>756.3531452348894</v>
+        <v>637.2329326635748</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12.31 segundos</t>
+          <t>9.38 segundos</t>
         </is>
       </c>
     </row>
@@ -650,18 +650,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[18, 26, 18, 25, 25]</t>
+          <t>[29, 24, 29, 6, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>610.5220226302893</v>
+        <v>628.1953140794993</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15.81 segundos</t>
+          <t>12.06 segundos</t>
         </is>
       </c>
     </row>
@@ -671,18 +671,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[18, 26, 18, 25, 25]</t>
+          <t>[29, 24, 29, 6, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>610.5220226302893</v>
+        <v>628.1953140794993</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.38 segundos</t>
+          <t>8.54 segundos</t>
         </is>
       </c>
     </row>
@@ -692,18 +692,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[18, 25, 18, 25, 25]</t>
+          <t>[29, 24, 29, 6, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>607.7211707558515</v>
+        <v>628.1953140794993</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.04 segundos</t>
+          <t>8.76 segundos</t>
         </is>
       </c>
     </row>
@@ -713,18 +713,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[29, 29, 19, 13, 27]</t>
+          <t>[17, 8, 4, 29, 0]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>944.6459271678667</v>
+        <v>921.8050539949847</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.23 segundos</t>
+          <t>11.27 segundos</t>
         </is>
       </c>
     </row>
@@ -734,18 +734,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[29, 29, 19, 13, 8]</t>
+          <t>[29, 8, 4, 29, 19]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>860.8565902042925</v>
+        <v>782.5074432434052</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12.52 segundos</t>
+          <t>7.54 segundos</t>
         </is>
       </c>
     </row>
@@ -755,18 +755,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[3, 29, 19, 30, 30]</t>
+          <t>[29, 8, 4, 29, 19]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>801.4108200185689</v>
+        <v>782.5074432434052</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.89 segundos</t>
+          <t>8.50 segundos</t>
         </is>
       </c>
     </row>
@@ -776,18 +776,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[16, 7, 16, 29, 31]</t>
+          <t>[29, 24, 29, 25, 9]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>656.1490671292927</v>
+        <v>685.3443148238365</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.34 segundos</t>
+          <t>13.44 segundos</t>
         </is>
       </c>
     </row>
@@ -797,18 +797,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[16, 7, 16, 29, 24]</t>
+          <t>[29, 24, 29, 25, 9]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>652.8577659149166</v>
+        <v>685.3443148238365</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13.76 segundos</t>
+          <t>8.63 segundos</t>
         </is>
       </c>
     </row>
@@ -818,18 +818,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[16, 7, 16, 29, 24]</t>
+          <t>[29, 24, 29, 15, 9]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>652.8577659149166</v>
+        <v>657.3081927645685</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.20 segundos</t>
+          <t>8.20 segundos</t>
         </is>
       </c>
     </row>
@@ -839,18 +839,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[16, 26, 25, 31, 3]</t>
+          <t>[27, 4, 0, 13, 0]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>792.8298963468076</v>
+        <v>764.5144436429993</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17.28 segundos</t>
+          <t>12.32 segundos</t>
         </is>
       </c>
     </row>
@@ -860,18 +860,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[16, 9, 31, 31, 3]</t>
+          <t>[11, 4, 0, 0, 11]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>652.3223258737335</v>
+        <v>744.0304384498064</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14.21 segundos</t>
+          <t>8.71 segundos</t>
         </is>
       </c>
     </row>
@@ -881,18 +881,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[16, 9, 31, 31, 3]</t>
+          <t>[11, 4, 0, 0, 11]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>652.3223258737335</v>
+        <v>744.0304384498064</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.98 segundos</t>
+          <t>8.81 segundos</t>
         </is>
       </c>
     </row>
@@ -902,18 +902,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 13, 5, 18, 7]</t>
+          <t>[31, 5, 6, 31, 31]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>792.8554795598354</v>
+        <v>741.0280250248692</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15.92 segundos</t>
+          <t>10.39 segundos</t>
         </is>
       </c>
     </row>
@@ -923,18 +923,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[10, 11, 4, 10, 17]</t>
+          <t>[31, 11, 17, 31, 31]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>738.4196843003388</v>
+        <v>645.4561618762922</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.53 segundos</t>
+          <t>8.32 segundos</t>
         </is>
       </c>
     </row>
@@ -944,18 +944,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 10, 17]</t>
+          <t>[31, 11, 17, 31, 31]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>709.7513417038922</v>
+        <v>645.4561618762922</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11.47 segundos</t>
+          <t>8.34 segundos</t>
         </is>
       </c>
     </row>
@@ -965,18 +965,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[24, 28, 17, 24, 26]</t>
+          <t>[31, 25, 31, 12, 31]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>702.4583052636711</v>
+        <v>615.2789907350623</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.51 segundos</t>
+          <t>12.21 segundos</t>
         </is>
       </c>
     </row>
@@ -986,18 +986,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[24, 3, 17, 24, 26]</t>
+          <t>[31, 2, 31, 8, 31]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>617.1380590752259</v>
+        <v>615.2789907350622</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12.45 segundos</t>
+          <t>8.58 segundos</t>
         </is>
       </c>
     </row>
@@ -1007,18 +1007,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[24, 30, 17, 24, 26]</t>
+          <t>[31, 2, 31, 8, 31]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>584.7619826237641</v>
+        <v>615.2789907350622</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11.88 segundos</t>
+          <t>8.28 segundos</t>
         </is>
       </c>
     </row>
@@ -1028,18 +1028,18 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[6, 26, 0, 12, 26]</t>
+          <t>[13, 6, 5, 29, 31]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>761.430784362382</v>
+        <v>793.4012345787432</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.42 segundos</t>
+          <t>11.98 segundos</t>
         </is>
       </c>
     </row>
@@ -1049,18 +1049,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[6, 26, 0, 12, 26]</t>
+          <t>[4, 19, 29, 29, 13]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>761.430784362382</v>
+        <v>740.0044014922465</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11.75 segundos</t>
+          <t>9.04 segundos</t>
         </is>
       </c>
     </row>
@@ -1070,18 +1070,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[6, 26, 0, 12, 26]</t>
+          <t>[4, 4, 29, 29, 25]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>761.430784362382</v>
+        <v>631.9139070324137</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12.22 segundos</t>
+          <t>7.43 segundos</t>
         </is>
       </c>
     </row>
@@ -1091,18 +1091,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[30, 25, 8, 30, 31]</t>
+          <t>[10, 1, 18, 25, 4]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>717.3134203970682</v>
+        <v>925.3984402924643</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.73 segundos</t>
+          <t>9.59 segundos</t>
         </is>
       </c>
     </row>
@@ -1112,18 +1112,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[30, 25, 10, 30, 19]</t>
+          <t>[18, 27, 18, 4, 4]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>650.8517697883511</v>
+        <v>654.3750641328345</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12.36 segundos</t>
+          <t>8.38 segundos</t>
         </is>
       </c>
     </row>
@@ -1133,18 +1133,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[30, 25, 10, 30, 30]</t>
+          <t>[18, 27, 18, 4, 4]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>613.0800854248301</v>
+        <v>654.3750641328345</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10.99 segundos</t>
+          <t>8.78 segundos</t>
         </is>
       </c>
     </row>
@@ -1154,18 +1154,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[31, 16, 25, 31, 17]</t>
+          <t>[2, 7, 29, 2, 17]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>695.5127233955105</v>
+        <v>769.6821022954002</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.03 segundos</t>
+          <t>11.22 segundos</t>
         </is>
       </c>
     </row>
@@ -1175,18 +1175,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[31, 1, 9, 31, 17]</t>
+          <t>[2, 29, 9, 2, 17]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>650.8517697883511</v>
+        <v>650.8517697883508</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12.49 segundos</t>
+          <t>9.52 segundos</t>
         </is>
       </c>
     </row>
@@ -1196,18 +1196,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[31, 1, 9, 31, 1]</t>
+          <t>[23, 29, 23, 29, 31]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>583.951185369161</v>
+        <v>641.403599323073</v>
       </c>
       <c r="D37" t="n">
         <v>13</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12.07 segundos</t>
+          <t>10.05 segundos</t>
         </is>
       </c>
     </row>
@@ -1217,18 +1217,18 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[12, 2, 25, 12, 2]</t>
+          <t>[0, 6, 19, 26, 7]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>623.8716593616098</v>
+        <v>765.7026073643867</v>
       </c>
       <c r="D38" t="n">
         <v>4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>15.90 segundos</t>
+          <t>11.62 segundos</t>
         </is>
       </c>
     </row>
@@ -1238,18 +1238,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[12, 2, 25, 12, 2]</t>
+          <t>[18, 7, 6, 6, 7]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>623.8716593616098</v>
+        <v>682.6270496201187</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12.58 segundos</t>
+          <t>9.18 segundos</t>
         </is>
       </c>
     </row>
@@ -1259,18 +1259,18 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[12, 2, 25, 12, 2]</t>
+          <t>[29, 0, 6, 6, 12]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>623.8716593616098</v>
+        <v>653.0151104645722</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.32 segundos</t>
+          <t>8.40 segundos</t>
         </is>
       </c>
     </row>
@@ -1280,18 +1280,18 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[13, 7, 13, 31, 24]</t>
+          <t>[4, 31, 18, 0, 10]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>652.8577659149166</v>
+        <v>922.5201941113844</v>
       </c>
       <c r="D41" t="n">
         <v>3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16.43 segundos</t>
+          <t>11.92 segundos</t>
         </is>
       </c>
     </row>
@@ -1301,18 +1301,18 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[13, 7, 13, 31, 24]</t>
+          <t>[0, 29, 18, 0, 9]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>652.8577659149166</v>
+        <v>649.9070763321287</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12.78 segundos</t>
+          <t>9.17 segundos</t>
         </is>
       </c>
     </row>
@@ -1322,18 +1322,18 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[13, 7, 13, 31, 24]</t>
+          <t>[0, 29, 18, 0, 9]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>652.8577659149166</v>
+        <v>649.9070763321287</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.08 segundos</t>
+          <t>8.42 segundos</t>
         </is>
       </c>
     </row>
@@ -1343,18 +1343,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[24, 0, 8, 24, 10]</t>
+          <t>[9, 9, 9, 26, 10]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>652.4352342173285</v>
+        <v>695.0080752893803</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17.39 segundos</t>
+          <t>12.17 segundos</t>
         </is>
       </c>
     </row>
@@ -1364,18 +1364,18 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[24, 30, 8, 24, 17]</t>
+          <t>[9, 3, 9, 16, 4]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>650.851769788351</v>
+        <v>617.4172855059593</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13.41 segundos</t>
+          <t>8.78 segundos</t>
         </is>
       </c>
     </row>
@@ -1385,18 +1385,18 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[24, 30, 8, 24, 26]</t>
+          <t>[9, 3, 9, 28, 11]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>584.7619826237641</v>
+        <v>605.8890668516817</v>
       </c>
       <c r="D46" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>10.97 segundos</t>
+          <t>7.50 segundos</t>
         </is>
       </c>
     </row>
@@ -1406,18 +1406,18 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[29, 25, 29, 9, 25]</t>
+          <t>[6, 31, 1, 17, 31]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>607.7961274850295</v>
+        <v>894.8693492773441</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16.25 segundos</t>
+          <t>12.19 segundos</t>
         </is>
       </c>
     </row>
@@ -1427,18 +1427,18 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[29, 25, 29, 9, 25]</t>
+          <t>[3, 27, 3, 3, 31]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>607.7961274850295</v>
+        <v>627.4841017458193</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10.48 segundos</t>
+          <t>8.88 segundos</t>
         </is>
       </c>
     </row>
@@ -1448,18 +1448,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[29, 25, 29, 9, 25]</t>
+          <t>[3, 24, 3, 3, 9]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>607.7961274850295</v>
+        <v>479.358066998272</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>11.57 segundos</t>
+          <t>8.92 segundos</t>
         </is>
       </c>
     </row>
@@ -1469,18 +1469,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[0, 4, 18, 0, 0]</t>
+          <t>[2, 8, 14, 26, 2]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>628.0273227550213</v>
+        <v>754.5252035774033</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13.97 segundos</t>
+          <t>11.59 segundos</t>
         </is>
       </c>
     </row>
@@ -1490,18 +1490,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[0, 4, 18, 0, 0]</t>
+          <t>[28, 18, 28, 0, 28]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>628.0273227550213</v>
+        <v>700.0335788781744</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12.22 segundos</t>
+          <t>8.52 segundos</t>
         </is>
       </c>
     </row>
@@ -1511,18 +1511,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[0, 31, 18, 0, 0]</t>
+          <t>[28, 18, 28, 0, 28]</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>613.08008542483</v>
+        <v>700.0335788781744</v>
       </c>
       <c r="D52" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>11.92 segundos</t>
+          <t>8.45 segundos</t>
         </is>
       </c>
     </row>
@@ -1532,18 +1532,18 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[3, 30, 3, 6, 24]</t>
+          <t>[10, 12, 12, 1, 29]</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>732.5761848742844</v>
+        <v>1005.595913821295</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16.08 segundos</t>
+          <t>11.81 segundos</t>
         </is>
       </c>
     </row>
@@ -1553,18 +1553,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[6, 0, 29, 6, 0]</t>
+          <t>[19, 28, 19, 8, 10]</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>591.4955829101477</v>
+        <v>685.256640825619</v>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>12.67 segundos</t>
+          <t>8.99 segundos</t>
         </is>
       </c>
     </row>
@@ -1574,18 +1574,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[6, 0, 29, 6, 0]</t>
+          <t>[19, 28, 19, 8, 15]</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>591.4955829101477</v>
+        <v>680.1966416035276</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>12.24 segundos</t>
+          <t>8.13 segundos</t>
         </is>
       </c>
     </row>
@@ -1595,18 +1595,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[24, 2, 24, 9, 24]</t>
+          <t>[12, 6, 5, 5, 25]</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>589.2140070307033</v>
+        <v>654.1685999198485</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16.13 segundos</t>
+          <t>12.08 segundos</t>
         </is>
       </c>
     </row>
@@ -1616,18 +1616,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[24, 2, 24, 9, 24]</t>
+          <t>[12, 6, 5, 5, 25]</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>589.2140070307033</v>
+        <v>654.1685999198485</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>11.48 segundos</t>
+          <t>7.91 segundos</t>
         </is>
       </c>
     </row>
@@ -1637,18 +1637,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[24, 2, 24, 9, 24]</t>
+          <t>[0, 6, 5, 5, 25]</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>589.2140070307033</v>
+        <v>633.3886837770573</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11.22 segundos</t>
+          <t>7.05 segundos</t>
         </is>
       </c>
     </row>
@@ -1658,18 +1658,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[5, 0, 0, 24, 5]</t>
+          <t>[1, 8, 25, 17, 1]</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>685.4152695425225</v>
+        <v>763.625019763607</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>15.94 segundos</t>
+          <t>11.76 segundos</t>
         </is>
       </c>
     </row>
@@ -1679,18 +1679,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[24, 0, 0, 24, 5]</t>
+          <t>[1, 8, 17, 17, 1]</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>627.4062618379006</v>
+        <v>624.0947101724872</v>
       </c>
       <c r="D60" t="n">
         <v>8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11.41 segundos</t>
+          <t>9.56 segundos</t>
         </is>
       </c>
     </row>
@@ -1700,18 +1700,18 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[24, 0, 3, 24, 5]</t>
+          <t>[1, 8, 17, 17, 1]</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>582.3490195021119</v>
+        <v>624.0947101724872</v>
       </c>
       <c r="D61" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12.17 segundos</t>
+          <t>9.58 segundos</t>
         </is>
       </c>
     </row>
@@ -1721,18 +1721,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[24, 25, 10, 31, 19]</t>
+          <t>[6, 0, 6, 29, 31]</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>804.4764953628312</v>
+        <v>623.7729906778302</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15.95 segundos</t>
+          <t>13.31 segundos</t>
         </is>
       </c>
     </row>
@@ -1742,18 +1742,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[24, 25, 10, 31, 19]</t>
+          <t>[6, 0, 6, 29, 31]</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>804.4764953628312</v>
+        <v>623.7729906778302</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11.88 segundos</t>
+          <t>10.72 segundos</t>
         </is>
       </c>
     </row>
@@ -1763,18 +1763,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[7, 27, 7, 3, 16]</t>
+          <t>[6, 0, 6, 29, 31]</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>750.9305819372843</v>
+        <v>623.7729906778302</v>
       </c>
       <c r="D64" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11.78 segundos</t>
+          <t>10.15 segundos</t>
         </is>
       </c>
     </row>
@@ -1784,18 +1784,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[23, 29, 23, 13, 15]</t>
+          <t>[31, 26, 26, 7, 2]</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>796.4604731412492</v>
+        <v>758.5993688058553</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17.20 segundos</t>
+          <t>13.55 segundos</t>
         </is>
       </c>
     </row>
@@ -1805,18 +1805,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[23, 29, 23, 13, 15]</t>
+          <t>[31, 26, 6, 31, 2]</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>796.4604731412492</v>
+        <v>620.7941976470595</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10.34 segundos</t>
+          <t>10.02 segundos</t>
         </is>
       </c>
     </row>
@@ -1826,18 +1826,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[29, 0, 14, 29, 5]</t>
+          <t>[31, 2, 6, 31, 2]</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>649.9070763321289</v>
+        <v>586.1871650874158</v>
       </c>
       <c r="D67" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>11.19 segundos</t>
+          <t>10.32 segundos</t>
         </is>
       </c>
     </row>
@@ -1847,18 +1847,18 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[4, 4, 13, 24, 26]</t>
+          <t>[1, 5, 1, 6, 1]</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>804.4329392785953</v>
+        <v>767.87582539383</v>
       </c>
       <c r="D68" t="n">
         <v>4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>15.36 segundos</t>
+          <t>12.43 segundos</t>
         </is>
       </c>
     </row>
@@ -1868,18 +1868,18 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[4, 28, 0, 0, 0]</t>
+          <t>[1, 28, 6, 6, 1]</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>584.7875991409136</v>
+        <v>696.0995045158115</v>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11.10 segundos</t>
+          <t>9.08 segundos</t>
         </is>
       </c>
     </row>
@@ -1889,18 +1889,18 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>[4, 28, 0, 0, 0]</t>
+          <t>[31, 11, 16, 16, 27]</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>584.7875991409136</v>
+        <v>664.3968486579437</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>10.31 segundos</t>
+          <t>6.83 segundos</t>
         </is>
       </c>
     </row>
@@ -1910,18 +1910,18 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[11, 3, 2, 18, 2]</t>
+          <t>[30, 10, 15, 2, 26]</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>792.9751831361273</v>
+        <v>825.4294155178641</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14.90 segundos</t>
+          <t>9.84 segundos</t>
         </is>
       </c>
     </row>
@@ -1931,18 +1931,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[11, 3, 2, 29, 2]</t>
+          <t>[2, 2, 14, 2, 26]</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>756.1824244393304</v>
+        <v>664.9158549210043</v>
       </c>
       <c r="D72" t="n">
         <v>7</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9.65 segundos</t>
+          <t>8.43 segundos</t>
         </is>
       </c>
     </row>
@@ -1952,18 +1952,18 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[11, 3, 2, 29, 2]</t>
+          <t>[2, 2, 8, 8, 4]</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>756.1824244393304</v>
+        <v>615.1431468143892</v>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>11.86 segundos</t>
+          <t>7.85 segundos</t>
         </is>
       </c>
     </row>
@@ -1973,18 +1973,18 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[15, 21, 15, 15, 28]</t>
+          <t>[30, 30, 30, 1, 7]</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>684.8263018300131</v>
+        <v>662.9935368259281</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>15.85 segundos</t>
+          <t>11.37 segundos</t>
         </is>
       </c>
     </row>
@@ -1994,18 +1994,18 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[17, 0, 17, 10, 0]</t>
+          <t>[30, 30, 30, 15, 31]</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>646.6168270920224</v>
+        <v>644.4300839680577</v>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>12.88 segundos</t>
+          <t>7.73 segundos</t>
         </is>
       </c>
     </row>
@@ -2015,18 +2015,18 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>[17, 0, 17, 10, 0]</t>
+          <t>[30, 26, 29, 30, 31]</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>646.6168270920224</v>
+        <v>564.5045104107461</v>
       </c>
       <c r="D76" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>10.02 segundos</t>
+          <t>9.00 segundos</t>
         </is>
       </c>
     </row>
@@ -2036,18 +2036,18 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>[5, 27, 19, 19, 28]</t>
+          <t>[2, 24, 31, 31, 4]</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>621.9004747712621</v>
+        <v>578.6775484402492</v>
       </c>
       <c r="D77" t="n">
         <v>4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>14.03 segundos</t>
+          <t>10.45 segundos</t>
         </is>
       </c>
     </row>
@@ -2057,18 +2057,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[5, 27, 19, 19, 28]</t>
+          <t>[2, 24, 31, 31, 4]</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>621.9004747712621</v>
+        <v>578.6775484402492</v>
       </c>
       <c r="D78" t="n">
         <v>4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>11.63 segundos</t>
+          <t>8.39 segundos</t>
         </is>
       </c>
     </row>
@@ -2078,18 +2078,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[5, 27, 19, 19, 28]</t>
+          <t>[2, 24, 31, 31, 4]</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>621.9004747712621</v>
+        <v>578.6775484402492</v>
       </c>
       <c r="D79" t="n">
         <v>4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>11.06 segundos</t>
+          <t>8.23 segundos</t>
         </is>
       </c>
     </row>
@@ -2099,18 +2099,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>[31, 5, 31, 14, 28]</t>
+          <t>[5, 0, 5, 18, 1]</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>791.6096606177399</v>
+        <v>617.4172855059593</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>15.49 segundos</t>
+          <t>10.28 segundos</t>
         </is>
       </c>
     </row>
@@ -2120,18 +2120,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[31, 5, 31, 31, 28]</t>
+          <t>[5, 0, 5, 18, 1]</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>679.9681387570566</v>
+        <v>617.4172855059593</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>12.10 segundos</t>
+          <t>8.26 segundos</t>
         </is>
       </c>
     </row>
@@ -2141,18 +2141,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[31, 24, 31, 31, 11]</t>
+          <t>[5, 0, 5, 18, 1]</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>479.3580669982718</v>
+        <v>617.4172855059593</v>
       </c>
       <c r="D82" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>12.15 segundos</t>
+          <t>8.23 segundos</t>
         </is>
       </c>
     </row>
@@ -2162,18 +2162,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[20, 26, 20, 31, 20]</t>
+          <t>[26, 28, 26, 26, 29]</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>579.8240831473222</v>
+        <v>494.6910114620277</v>
       </c>
       <c r="D83" t="n">
         <v>4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16.75 segundos</t>
+          <t>11.11 segundos</t>
         </is>
       </c>
     </row>
@@ -2183,18 +2183,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[20, 26, 20, 31, 20]</t>
+          <t>[26, 28, 26, 26, 29]</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>579.8240831473222</v>
+        <v>494.6910114620277</v>
       </c>
       <c r="D84" t="n">
         <v>4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>12.39 segundos</t>
+          <t>10.02 segundos</t>
         </is>
       </c>
     </row>
@@ -2204,18 +2204,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[20, 26, 20, 20, 20]</t>
+          <t>[26, 28, 26, 26, 29]</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>459.4619885894684</v>
+        <v>494.6910114620277</v>
       </c>
       <c r="D85" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>12.83 segundos</t>
+          <t>8.12 segundos</t>
         </is>
       </c>
     </row>
@@ -2225,18 +2225,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[2, 13, 12, 30, 18]</t>
+          <t>[2, 11, 22, 31, 16]</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>847.8604480162528</v>
+        <v>953.2536154986531</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17.38 segundos</t>
+          <t>11.48 segundos</t>
         </is>
       </c>
     </row>
@@ -2246,18 +2246,18 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[16, 0, 16, 7, 27]</t>
+          <t>[12, 1, 5, 5, 18]</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>651.0837629184591</v>
+        <v>784.8686584715633</v>
       </c>
       <c r="D87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>12.97 segundos</t>
+          <t>7.72 segundos</t>
         </is>
       </c>
     </row>
@@ -2267,18 +2267,18 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[16, 0, 16, 7, 27]</t>
+          <t>[12, 30, 5, 5, 21]</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>651.0837629184591</v>
+        <v>782.3592118449275</v>
       </c>
       <c r="D88" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>11.60 segundos</t>
+          <t>6.99 segundos</t>
         </is>
       </c>
     </row>
@@ -2288,18 +2288,18 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 20, 16]</t>
+          <t>[23, 24, 23, 8, 17]</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>817.7707929847866</v>
+        <v>799.2311471950018</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>14.98 segundos</t>
+          <t>11.87 segundos</t>
         </is>
       </c>
     </row>
@@ -2309,18 +2309,18 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 16]</t>
+          <t>[23, 24, 23, 8, 17]</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>544.5151144812581</v>
+        <v>799.2311471950018</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>14.40 segundos</t>
+          <t>7.90 segundos</t>
         </is>
       </c>
     </row>
@@ -2330,18 +2330,18 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 16]</t>
+          <t>[23, 24, 23, 8, 31]</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>544.5151144812581</v>
+        <v>776.3396603813572</v>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>11.90 segundos</t>
+          <t>7.94 segundos</t>
         </is>
       </c>
     </row>
@@ -2351,18 +2351,18 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[9, 13, 19, 19, 5]</t>
+          <t>[18, 3, 28, 8, 7]</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>843.7338479457957</v>
+        <v>933.3675704589662</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16.34 segundos</t>
+          <t>10.71 segundos</t>
         </is>
       </c>
     </row>
@@ -2372,18 +2372,18 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[17, 27, 25, 25, 27]</t>
+          <t>[28, 26, 17, 25, 26]</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>603.9926747370439</v>
+        <v>877.5859088336709</v>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>11.48 segundos</t>
+          <t>8.32 segundos</t>
         </is>
       </c>
     </row>
@@ -2393,18 +2393,18 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>[17, 27, 25, 25, 27]</t>
+          <t>[30, 25, 25, 9, 16]</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>603.9926747370439</v>
+        <v>754.7681407768206</v>
       </c>
       <c r="D94" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>10.14 segundos</t>
+          <t>8.02 segundos</t>
         </is>
       </c>
     </row>
@@ -2414,18 +2414,18 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[13, 13, 4, 4, 18]</t>
+          <t>[30, 19, 5, 30, 25]</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>836.8949843947177</v>
+        <v>712.7148711178182</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14.89 segundos</t>
+          <t>11.76 segundos</t>
         </is>
       </c>
     </row>
@@ -2435,18 +2435,18 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[6, 28, 4, 4, 6]</t>
+          <t>[31, 26, 17, 17, 31]</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>615.8011004849803</v>
+        <v>618.4413485637045</v>
       </c>
       <c r="D96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>12.43 segundos</t>
+          <t>7.26 segundos</t>
         </is>
       </c>
     </row>
@@ -2456,18 +2456,18 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[4, 28, 4, 4, 6]</t>
+          <t>[31, 26, 17, 17, 31]</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>459.4619885894684</v>
+        <v>618.4413485637045</v>
       </c>
       <c r="D97" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>11.50 segundos</t>
+          <t>7.61 segundos</t>
         </is>
       </c>
     </row>
@@ -2477,18 +2477,18 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[31, 10, 27, 4, 27]</t>
+          <t>[1, 1, 0, 25, 1]</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>843.1231347434178</v>
+        <v>751.6508241276836</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>15.27 segundos</t>
+          <t>10.01 segundos</t>
         </is>
       </c>
     </row>
@@ -2498,18 +2498,18 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[31, 10, 27, 18, 27]</t>
+          <t>[9, 1, 0, 25, 1]</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>790.7446230517668</v>
+        <v>726.8026538089596</v>
       </c>
       <c r="D99" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>12.29 segundos</t>
+          <t>8.42 segundos</t>
         </is>
       </c>
     </row>
@@ -2519,18 +2519,18 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>[31, 10, 27, 18, 27]</t>
+          <t>[9, 1, 0, 25, 1]</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>790.7446230517668</v>
+        <v>726.8026538089596</v>
       </c>
       <c r="D100" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>13.12 segundos</t>
+          <t>7.97 segundos</t>
         </is>
       </c>
     </row>
@@ -2540,18 +2540,18 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[25, 26, 3, 9, 2]</t>
+          <t>[28, 29, 27, 27, 29]</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>929.4784903516644</v>
+        <v>525.5163048844477</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>14.62 segundos</t>
+          <t>10.34 segundos</t>
         </is>
       </c>
     </row>
@@ -2561,18 +2561,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[25, 10, 25, 9, 25]</t>
+          <t>[28, 29, 27, 27, 29]</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>696.3937072465774</v>
+        <v>525.5163048844477</v>
       </c>
       <c r="D102" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>11.99 segundos</t>
+          <t>9.40 segundos</t>
         </is>
       </c>
     </row>
@@ -2582,18 +2582,18 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[25, 29, 25, 9, 25]</t>
+          <t>[28, 29, 27, 27, 29]</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>603.9143884297888</v>
+        <v>525.5163048844477</v>
       </c>
       <c r="D103" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>12.61 segundos</t>
+          <t>9.07 segundos</t>
         </is>
       </c>
     </row>
@@ -2603,18 +2603,18 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>[24, 9, 19, 24, 30]</t>
+          <t>[1, 10, 1, 29, 1]</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>757.5511448933073</v>
+        <v>669.4315054231704</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>17.60 segundos</t>
+          <t>10.53 segundos</t>
         </is>
       </c>
     </row>
@@ -2624,18 +2624,18 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[24, 30, 14, 24, 30]</t>
+          <t>[1, 29, 1, 14, 1]</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>616.327261820623</v>
+        <v>615.2789907350625</v>
       </c>
       <c r="D105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>10.02 segundos</t>
+          <t>8.37 segundos</t>
         </is>
       </c>
     </row>
@@ -2645,18 +2645,18 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[24, 30, 14, 24, 30]</t>
+          <t>[1, 26, 1, 25, 1]</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>616.327261820623</v>
+        <v>587.1050975975683</v>
       </c>
       <c r="D106" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>10.88 segundos</t>
+          <t>8.08 segundos</t>
         </is>
       </c>
     </row>
@@ -2666,18 +2666,18 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[31, 6, 5, 5, 11]</t>
+          <t>[29, 30, 24, 10, 2]</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>656.5280571326069</v>
+        <v>812.2487463908906</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15.41 segundos</t>
+          <t>11.08 segundos</t>
         </is>
       </c>
     </row>
@@ -2687,18 +2687,18 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[31, 6, 5, 5, 11]</t>
+          <t>[10, 30, 24, 10, 30]</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>656.5280571326069</v>
+        <v>623.8716593616094</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>11.41 segundos</t>
+          <t>8.07 segundos</t>
         </is>
       </c>
     </row>
@@ -2708,18 +2708,18 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[31, 6, 5, 5, 11]</t>
+          <t>[10, 30, 24, 10, 30]</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>656.5280571326069</v>
+        <v>623.8716593616094</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>11.18 segundos</t>
+          <t>8.18 segundos</t>
         </is>
       </c>
     </row>
@@ -2729,18 +2729,18 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[27, 1, 4, 4, 3]</t>
+          <t>[28, 22, 19, 19, 28]</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>873.477001295767</v>
+        <v>902.0492079493375</v>
       </c>
       <c r="D110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>14.74 segundos</t>
+          <t>10.17 segundos</t>
         </is>
       </c>
     </row>
@@ -2750,18 +2750,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[22, 29, 6, 22, 22]</t>
+          <t>[3, 27, 19, 19, 28]</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>723.4106611775105</v>
+        <v>621.9004747712626</v>
       </c>
       <c r="D111" t="n">
         <v>8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>10.08 segundos</t>
+          <t>8.05 segundos</t>
         </is>
       </c>
     </row>
@@ -2771,18 +2771,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[22, 29, 22, 22, 22]</t>
+          <t>[3, 27, 19, 19, 28]</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>459.4619885894684</v>
+        <v>621.9004747712626</v>
       </c>
       <c r="D112" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>11.12 segundos</t>
+          <t>9.73 segundos</t>
         </is>
       </c>
     </row>
@@ -2792,18 +2792,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[6, 28, 2, 2, 2]</t>
+          <t>[6, 12, 6, 19, 8]</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>584.7875991409136</v>
+        <v>647.8933805180666</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>15.63 segundos</t>
+          <t>11.97 segundos</t>
         </is>
       </c>
     </row>
@@ -2813,18 +2813,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[6, 2, 2, 2, 2]</t>
+          <t>[6, 1, 6, 19, 8]</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>583.6375571912222</v>
+        <v>615.5173040666044</v>
       </c>
       <c r="D114" t="n">
         <v>5</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>11.56 segundos</t>
+          <t>8.97 segundos</t>
         </is>
       </c>
     </row>
@@ -2834,18 +2834,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[7, 2, 2, 2, 2]</t>
+          <t>[6, 1, 6, 19, 8]</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>568.3021842508629</v>
+        <v>615.5173040666044</v>
       </c>
       <c r="D115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>11.05 segundos</t>
+          <t>8.11 segundos</t>
         </is>
       </c>
     </row>
@@ -2855,18 +2855,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[5, 5, 14, 26, 6]</t>
+          <t>[2, 0, 2, 27, 9]</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>811.4100082011225</v>
+        <v>736.2475973007254</v>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>16.60 segundos</t>
+          <t>10.27 segundos</t>
         </is>
       </c>
     </row>
@@ -2876,18 +2876,18 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[27, 0, 26, 27, 17]</t>
+          <t>[14, 0, 27, 27, 6]</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>787.258477239218</v>
+        <v>649.0591281073408</v>
       </c>
       <c r="D117" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>12.65 segundos</t>
+          <t>7.41 segundos</t>
         </is>
       </c>
     </row>
@@ -2897,18 +2897,18 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[15, 0, 7, 25, 15]</t>
+          <t>[14, 0, 27, 27, 6]</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>776.7266599516915</v>
+        <v>649.0591281073408</v>
       </c>
       <c r="D118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>10.85 segundos</t>
+          <t>7.23 segundos</t>
         </is>
       </c>
     </row>
@@ -2918,18 +2918,18 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>[2, 24, 17, 2, 30]</t>
+          <t>[1, 26, 1, 13, 1]</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>649.1123004481256</v>
+        <v>615.2789907350625</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>16.35 segundos</t>
+          <t>10.09 segundos</t>
         </is>
       </c>
     </row>
@@ -2939,18 +2939,18 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[2, 24, 17, 2, 30]</t>
+          <t>[1, 26, 1, 5, 1]</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>649.1123004481256</v>
+        <v>592.5323893619909</v>
       </c>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>12.03 segundos</t>
+          <t>8.02 segundos</t>
         </is>
       </c>
     </row>
@@ -2960,18 +2960,18 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[2, 24, 17, 2, 2]</t>
+          <t>[1, 26, 1, 5, 1]</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>613.08008542483</v>
+        <v>592.5323893619909</v>
       </c>
       <c r="D121" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>10.98 segundos</t>
+          <t>7.72 segundos</t>
         </is>
       </c>
     </row>
@@ -2981,18 +2981,18 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[4, 12, 30, 30, 0]</t>
+          <t>[4, 4, 31, 4, 9]</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>710.8915228071769</v>
+        <v>670.4156843421083</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>16.51 segundos</t>
+          <t>11.86 segundos</t>
         </is>
       </c>
     </row>
@@ -3002,18 +3002,18 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>[4, 12, 30, 30, 0]</t>
+          <t>[4, 4, 31, 4, 26]</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>710.8915228071769</v>
+        <v>644.1421496609248</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>11.21 segundos</t>
+          <t>8.03 segundos</t>
         </is>
       </c>
     </row>
@@ -3023,18 +3023,18 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>[15, 0, 30, 30, 0]</t>
+          <t>[4, 4, 31, 4, 26]</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>615.4793135958349</v>
+        <v>644.1421496609248</v>
       </c>
       <c r="D124" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>11.57 segundos</t>
+          <t>6.81 segundos</t>
         </is>
       </c>
     </row>
@@ -3044,18 +3044,18 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>[10, 1, 18, 10, 1]</t>
+          <t>[26, 16, 6, 6, 8]</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>644.6453646216891</v>
+        <v>721.6817487832336</v>
       </c>
       <c r="D125" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>14.23 segundos</t>
+          <t>11.56 segundos</t>
         </is>
       </c>
     </row>
@@ -3065,18 +3065,18 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[10, 1, 24, 10, 1]</t>
+          <t>[17, 7, 6, 6, 8]</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>623.8716593616098</v>
+        <v>654.2164881076977</v>
       </c>
       <c r="D126" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>11.77 segundos</t>
+          <t>8.05 segundos</t>
         </is>
       </c>
     </row>
@@ -3086,18 +3086,18 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[10, 1, 24, 10, 1]</t>
+          <t>[17, 7, 6, 6, 8]</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>623.8716593616098</v>
+        <v>654.2164881076977</v>
       </c>
       <c r="D127" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>10.76 segundos</t>
+          <t>6.91 segundos</t>
         </is>
       </c>
     </row>
@@ -3107,18 +3107,18 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[2, 11, 16, 30, 26]</t>
+          <t>[29, 24, 24, 23, 23]</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>821.5500569055391</v>
+        <v>724.9710041932276</v>
       </c>
       <c r="D128" t="n">
         <v>3</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>14.07 segundos</t>
+          <t>11.27 segundos</t>
         </is>
       </c>
     </row>
@@ -3128,18 +3128,18 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[2, 13, 13, 30, 26]</t>
+          <t>[29, 24, 24, 23, 23]</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>817.8028758749615</v>
+        <v>724.9710041932276</v>
       </c>
       <c r="D129" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>9.20 segundos</t>
+          <t>7.47 segundos</t>
         </is>
       </c>
     </row>
@@ -3149,18 +3149,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[13, 24, 13, 30, 2]</t>
+          <t>[29, 24, 24, 23, 31]</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>649.5945681485239</v>
+        <v>695.1503247446203</v>
       </c>
       <c r="D130" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>11.91 segundos</t>
+          <t>9.37 segundos</t>
         </is>
       </c>
     </row>
@@ -3170,18 +3170,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[17, 6, 24, 17, 1]</t>
+          <t>[27, 9, 15, 3, 9]</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>660.7146716395082</v>
+        <v>798.0786838158488</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>15.65 segundos</t>
+          <t>12.53 segundos</t>
         </is>
       </c>
     </row>
@@ -3191,18 +3191,18 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[17, 28, 1, 17, 24]</t>
+          <t>[27, 9, 15, 3, 9]</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>657.0069377844931</v>
+        <v>798.0786838158488</v>
       </c>
       <c r="D132" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>9.04 segundos</t>
+          <t>7.15 segundos</t>
         </is>
       </c>
     </row>
@@ -3212,18 +3212,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[17, 28, 1, 17, 24]</t>
+          <t>[27, 4, 18, 18, 31]</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>657.0069377844931</v>
+        <v>797.1621822887727</v>
       </c>
       <c r="D133" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>11.22 segundos</t>
+          <t>7.70 segundos</t>
         </is>
       </c>
     </row>
@@ -3233,18 +3233,18 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[2, 6, 31, 11, 2]</t>
+          <t>[19, 7, 26, 19, 0]</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>773.4663613874823</v>
+        <v>660.714671639508</v>
       </c>
       <c r="D134" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>15.04 segundos</t>
+          <t>11.25 segundos</t>
         </is>
       </c>
     </row>
@@ -3254,18 +3254,18 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[2, 1, 31, 11, 2]</t>
+          <t>[19, 7, 26, 19, 0]</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>767.2214188577072</v>
+        <v>660.714671639508</v>
       </c>
       <c r="D135" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>13.32 segundos</t>
+          <t>8.17 segundos</t>
         </is>
       </c>
     </row>
@@ -3275,18 +3275,18 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[2, 1, 31, 6, 2]</t>
+          <t>[19, 7, 26, 19, 0]</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>743.2866788218446</v>
+        <v>660.714671639508</v>
       </c>
       <c r="D136" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>8.44 segundos</t>
+          <t>6.90 segundos</t>
         </is>
       </c>
     </row>
@@ -3296,18 +3296,18 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[8, 31, 0, 8, 6]</t>
+          <t>[23, 24, 5, 5, 13]</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>765.0006328376103</v>
+        <v>794.3268694550694</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>14.72 segundos</t>
+          <t>10.20 segundos</t>
         </is>
       </c>
     </row>
@@ -3317,18 +3317,18 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>[8, 31, 0, 6, 8]</t>
+          <t>[27, 12, 5, 5, 13]</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>754.1884821618312</v>
+        <v>726.3444066681798</v>
       </c>
       <c r="D138" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>10.41 segundos</t>
+          <t>8.24 segundos</t>
         </is>
       </c>
     </row>
@@ -3338,18 +3338,18 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[8, 31, 0, 6, 8]</t>
+          <t>[19, 12, 5, 5, 13]</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>754.1884821618312</v>
+        <v>686.283071456265</v>
       </c>
       <c r="D139" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>11.17 segundos</t>
+          <t>7.68 segundos</t>
         </is>
       </c>
     </row>
@@ -3359,18 +3359,18 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>[9, 22, 9, 27, 29]</t>
+          <t>[26, 31, 17, 26, 4]</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>817.3396506004119</v>
+        <v>797.4057514356251</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>14.34 segundos</t>
+          <t>11.68 segundos</t>
         </is>
       </c>
     </row>
@@ -3380,18 +3380,18 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[9, 5, 9, 27, 29]</t>
+          <t>[26, 1, 26, 26, 4]</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>780.96395516916</v>
+        <v>586.4696481515899</v>
       </c>
       <c r="D141" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>11.61 segundos</t>
+          <t>9.07 segundos</t>
         </is>
       </c>
     </row>
@@ -3401,18 +3401,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[9, 4, 9, 27, 29]</t>
+          <t>[26, 5, 26, 26, 15]</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>623.7729906778309</v>
+        <v>511.7341434497342</v>
       </c>
       <c r="D142" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>11.78 segundos</t>
+          <t>8.50 segundos</t>
         </is>
       </c>
     </row>
@@ -3422,18 +3422,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[11, 11, 11, 8, 7]</t>
+          <t>[6, 31, 0, 0, 5]</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>876.5121300049924</v>
+        <v>729.9423335580105</v>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>14.51 segundos</t>
+          <t>10.31 segundos</t>
         </is>
       </c>
     </row>
@@ -3443,18 +3443,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[11, 11, 11, 30, 7]</t>
+          <t>[6, 4, 0, 0, 5]</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>707.4664884606975</v>
+        <v>722.7066793708436</v>
       </c>
       <c r="D144" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>10.72 segundos</t>
+          <t>6.63 segundos</t>
         </is>
       </c>
     </row>
@@ -3464,18 +3464,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[11, 11, 11, 30, 7]</t>
+          <t>[6, 4, 0, 0, 5]</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>707.4664884606975</v>
+        <v>722.7066793708436</v>
       </c>
       <c r="D145" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>7.86 segundos</t>
+          <t>7.83 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,39 +461,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[27, 10, 17, 27, 11]</t>
+          <t>[26, 3, 12, 12, 0]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>656.4216158515105</v>
+        <v>771.5084298112616</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.33 segundos</t>
+          <t>12.86 segundos</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[27, 10, 17, 27, 11]</t>
+          <t>[3, 3, 24, 12, 4]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>656.4216158515105</v>
+        <v>779.1890764678501</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.87 segundos</t>
+          <t>9.53 segundos</t>
         </is>
       </c>
     </row>
@@ -503,39 +503,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[30, 25, 30, 28, 30]</t>
+          <t>[17, 12, 12, 11, 30]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>441.9830741652839</v>
+        <v>810.4600380477424</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.40 segundos</t>
+          <t>9.88 segundos</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[30, 25, 30, 28, 30]</t>
+          <t>[0, 13, 13, 13, 24]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>441.9830741652839</v>
+        <v>692.965837546738</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.38 segundos</t>
+          <t>10.12 segundos</t>
         </is>
       </c>
     </row>
@@ -545,39 +545,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[30, 9, 30, 16, 24]</t>
+          <t>[8, 2, 0, 0, 28]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>660.5713905309615</v>
+        <v>725.0770825865833</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.57 segundos</t>
+          <t>10.64 segundos</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[30, 9, 30, 16, 24]</t>
+          <t>[28, 27, 28, 16, 28]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>660.5713905309615</v>
+        <v>627.9862582846279</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.63 segundos</t>
+          <t>10.65 segundos</t>
         </is>
       </c>
     </row>
@@ -587,39 +587,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[26, 13, 19, 19, 7]</t>
+          <t>[9, 30, 15, 1, 9]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>693.5097273430129</v>
+        <v>775.7512598658383</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.74 segundos</t>
+          <t>10.69 segundos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[26, 6, 19, 19, 7]</t>
+          <t>[2, 3, 6, 15, 24]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>635.2721139594706</v>
+        <v>927.9499518667759</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8.66 segundos</t>
+          <t>9.74 segundos</t>
         </is>
       </c>
     </row>
@@ -629,39 +629,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[30, 25, 1, 16, 1]</t>
+          <t>[6, 0, 6, 27, 9]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>802.2245819067537</v>
+        <v>751.7613108564615</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.04 segundos</t>
+          <t>10.94 segundos</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[30, 7, 18, 30, 2]</t>
+          <t>[14, 2, 26, 14, 2]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>653.1702740985215</v>
+        <v>623.8716593616093</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.40 segundos</t>
+          <t>10.47 segundos</t>
         </is>
       </c>
     </row>
@@ -671,39 +671,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[13, 24, 6, 19, 25]</t>
+          <t>[8, 15, 8, 3, 5]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>795.703842141739</v>
+        <v>851.5135581802672</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.43 segundos</t>
+          <t>9.76 segundos</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[14, 25, 4, 30, 26]</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>753.3063682620318</v>
+      </c>
+      <c r="D13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>[13, 24, 6, 31, 8]</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>792.3197668069367</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9</v>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9.02 segundos</t>
+          <t>11.05 segundos</t>
         </is>
       </c>
     </row>
@@ -713,39 +713,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[10, 24, 25, 10, 29]</t>
+          <t>[0, 6, 0, 30, 3]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>732.8804740131981</v>
+        <v>750.47810287213</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10.98 segundos</t>
+          <t>9.45 segundos</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[10, 28, 25, 10, 29]</t>
+          <t>[3, 5, 16, 31, 9]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>700.77179220684</v>
+        <v>950.7377370908143</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.90 segundos</t>
+          <t>9.00 segundos</t>
         </is>
       </c>
     </row>
@@ -755,291 +755,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[19, 11, 4, 28, 4]</t>
+          <t>[26, 2, 25, 11, 2]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>824.5306145040977</v>
+        <v>868.1466344346644</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.97 segundos</t>
+          <t>10.58 segundos</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[5, 28, 28, 28, 11]</t>
+          <t>[6, 24, 0, 6, 17]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>685.5496142924079</v>
+        <v>650.5015299929699</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8.50 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>[7, 0, 20, 31, 1]</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>854.9523547138542</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>10.41 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>[6, 0, 16, 31, 1]</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>752.3309681761787</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>8.63 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>[16, 26, 16, 10, 5]</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>680.1966416035275</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>11.83 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>[16, 26, 16, 10, 5]</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>680.1966416035275</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>8.50 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>[5, 2, 12, 18, 7]</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>796.6380454296855</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>10.46 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>[18, 2, 12, 18, 5]</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>793.23139762288</v>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>8.13 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>[24, 29, 30, 30, 29]</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>652.4825433324514</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>11.52 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>[24, 25, 30, 24, 24]</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>483.7141957160432</v>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>8.02 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>[19, 31, 19, 24, 20]</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>815.9054745605378</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>10.91 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>[19, 31, 19, 24, 2]</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>753.9754389433098</v>
-      </c>
-      <c r="D27" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>8.15 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>[14, 31, 8, 14, 2]</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>657.0069377844929</v>
-      </c>
-      <c r="D28" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>10.77 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>[14, 31, 8, 14, 2]</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>657.0069377844929</v>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>8.24 segundos</t>
+          <t>9.38 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,102 +461,102 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[26, 3, 12, 12, 0]</t>
+          <t>[14, 28, 24, 2, 24]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>771.5084298112616</v>
+        <v>752.6703967924235</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.86 segundos</t>
+          <t>23.93 segundos</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[3, 3, 24, 12, 4]</t>
+          <t>[9, 28, 24, 2, 24]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>779.1890764678501</v>
+        <v>722.068323337419</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.53 segundos</t>
+          <t>17.07 segundos</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[17, 12, 12, 11, 30]</t>
+          <t>[31, 25, 24, 24, 0]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>810.4600380477424</v>
+        <v>628.1174956201863</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.88 segundos</t>
+          <t>16.71 segundos</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[0, 13, 13, 13, 24]</t>
+          <t>[31, 25, 24, 24, 0]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>692.965837546738</v>
+        <v>628.1174956201863</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.12 segundos</t>
+          <t>17.35 segundos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[8, 2, 0, 0, 28]</t>
+          <t>[31, 25, 24, 24, 0]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>725.0770825865833</v>
+        <v>628.1174956201863</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.64 segundos</t>
+          <t>10.97 segundos</t>
         </is>
       </c>
     </row>
@@ -566,102 +566,102 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[28, 27, 28, 16, 28]</t>
+          <t>[17, 2, 27, 17, 7]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>627.9862582846279</v>
+        <v>657.4514738731154</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.65 segundos</t>
+          <t>17.17 segundos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[9, 30, 15, 1, 9]</t>
+          <t>[17, 2, 27, 17, 7]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>775.7512598658383</v>
+        <v>657.4514738731154</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.69 segundos</t>
+          <t>17.76 segundos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[2, 3, 6, 15, 24]</t>
+          <t>[17, 2, 27, 17, 7]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>927.9499518667759</v>
+        <v>657.4514738731154</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9.74 segundos</t>
+          <t>16.69 segundos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[6, 0, 6, 27, 9]</t>
+          <t>[17, 2, 27, 17, 7]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>751.7613108564615</v>
+        <v>657.4514738731154</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.94 segundos</t>
+          <t>11.06 segundos</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[14, 2, 26, 14, 2]</t>
+          <t>[17, 2, 27, 17, 7]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>623.8716593616093</v>
+        <v>657.4514738731154</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.47 segundos</t>
+          <t>15.44 segundos</t>
         </is>
       </c>
     </row>
@@ -671,102 +671,102 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[8, 15, 8, 3, 5]</t>
+          <t>[12, 26, 0, 6, 27]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>851.5135581802672</v>
+        <v>755.2400991205897</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9.76 segundos</t>
+          <t>14.49 segundos</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[14, 25, 4, 30, 26]</t>
+          <t>[8, 26, 0, 0, 26]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>753.3063682620318</v>
+        <v>583.103237144373</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.05 segundos</t>
+          <t>12.38 segundos</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[0, 6, 0, 30, 3]</t>
+          <t>[8, 26, 0, 0, 26]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>750.47810287213</v>
+        <v>583.103237144373</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9.45 segundos</t>
+          <t>11.13 segundos</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[3, 5, 16, 31, 9]</t>
+          <t>[8, 26, 0, 0, 26]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>950.7377370908143</v>
+        <v>583.103237144373</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9.00 segundos</t>
+          <t>14.76 segundos</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[26, 2, 25, 11, 2]</t>
+          <t>[8, 26, 0, 0, 26]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>868.1466344346644</v>
+        <v>583.103237144373</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.58 segundos</t>
+          <t>10.65 segundos</t>
         </is>
       </c>
     </row>
@@ -776,18 +776,102 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[6, 24, 0, 6, 17]</t>
+          <t>[24, 31, 13, 5, 24]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>650.5015299929699</v>
+        <v>752.7512005809456</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.38 segundos</t>
+          <t>13.26 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[31, 10, 2, 2, 24]</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>714.8782117940392</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>19.47 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>[31, 10, 2, 2, 24]</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>714.8782117940392</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>13.17 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[31, 10, 2, 2, 19]</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>685.3911869160343</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>12.96 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[31, 10, 2, 2, 19]</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>685.3911869160343</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>15.04 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,6 +875,111 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>[8, 29, 11, 11, 4]</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>791.2585298170588</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>21.48 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>[8, 29, 8, 11, 4]</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>786.7753405517552</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>13.19 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>[8, 29, 8, 11, 4]</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>786.7753405517552</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>11.83 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[8, 29, 8, 31, 30]</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>739.8301101812643</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>15.61 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>[8, 29, 8, 28, 16]</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>652.1544263254081</v>
+      </c>
+      <c r="D26" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>18.14 segundos</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[14, 28, 24, 2, 24]</t>
+          <t>[30, 23, 30, 3, 5]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>752.6703967924235</v>
+        <v>60.76263738453761</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.93 segundos</t>
+          <t>28.33 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[9, 28, 24, 2, 24]</t>
+          <t>[30, 23, 30, 3, 5]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>722.068323337419</v>
+        <v>60.76263738453761</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.07 segundos</t>
+          <t>24.59 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[31, 25, 24, 24, 0]</t>
+          <t>[30, 30, 30, 3, 5]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>628.1174956201863</v>
+        <v>60.09135300228709</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.71 segundos</t>
+          <t>24.50 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[31, 25, 24, 24, 0]</t>
+          <t>[30, 30, 30, 5, 5]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>628.1174956201863</v>
+        <v>59.01519600909134</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.35 segundos</t>
+          <t>24.21 segundos</t>
         </is>
       </c>
     </row>
@@ -545,438 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[31, 25, 24, 24, 0]</t>
+          <t>[30, 6, 30, 5, 5]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>628.1174956201863</v>
+        <v>54.23416989278468</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.97 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[17, 2, 27, 17, 7]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>657.4514738731154</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>17.17 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[17, 2, 27, 17, 7]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>657.4514738731154</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>17.76 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[17, 2, 27, 17, 7]</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>657.4514738731154</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>16.69 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[17, 2, 27, 17, 7]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>657.4514738731154</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>11.06 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[17, 2, 27, 17, 7]</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>657.4514738731154</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>15.44 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>[12, 26, 0, 6, 27]</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>755.2400991205897</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>14.49 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>[8, 26, 0, 0, 26]</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>583.103237144373</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>12.38 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>[8, 26, 0, 0, 26]</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>583.103237144373</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>11.13 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>[8, 26, 0, 0, 26]</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>583.103237144373</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>14.76 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>[8, 26, 0, 0, 26]</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>583.103237144373</v>
-      </c>
-      <c r="D16" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>10.65 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>[24, 31, 13, 5, 24]</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>752.7512005809456</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>13.26 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>[31, 10, 2, 2, 24]</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>714.8782117940392</v>
-      </c>
-      <c r="D18" t="n">
-        <v>9</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>19.47 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>[31, 10, 2, 2, 24]</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>714.8782117940392</v>
-      </c>
-      <c r="D19" t="n">
-        <v>9</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>13.17 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>[31, 10, 2, 2, 19]</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>685.3911869160343</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>12.96 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>[31, 10, 2, 2, 19]</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>685.3911869160343</v>
-      </c>
-      <c r="D21" t="n">
-        <v>16</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>15.04 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>[8, 29, 11, 11, 4]</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>791.2585298170588</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>21.48 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>[8, 29, 8, 11, 4]</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>786.7753405517552</v>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>13.19 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>[8, 29, 8, 11, 4]</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>786.7753405517552</v>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>11.83 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>[8, 29, 8, 31, 30]</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>739.8301101812643</v>
-      </c>
-      <c r="D25" t="n">
-        <v>16</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>15.61 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>[8, 29, 8, 28, 16]</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>652.1544263254081</v>
-      </c>
-      <c r="D26" t="n">
-        <v>20</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>18.14 segundos</t>
+          <t>23.55 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[29, 1, 6, 22, 24]</t>
+          <t>[7, 19, 13, 24, 30]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.57928390723568</v>
+        <v>64.81144685131851</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.02 segundos</t>
+          <t>25.70 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[29, 24, 11, 22, 24]</t>
+          <t>[11, 3, 11, 27, 12]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74.36677778179499</v>
+        <v>64.50937114362654</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.69 segundos</t>
+          <t>14.60 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[29, 24, 22, 29, 24]</t>
+          <t>[23, 17, 16, 31, 17]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>53.44821975927021</v>
+        <v>64.01259582259932</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28.66 segundos</t>
+          <t>12.87 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[29, 24, 22, 29, 24]</t>
+          <t>[23, 17, 16, 31, 17]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53.44821975927021</v>
+        <v>64.01259582259932</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.25 segundos</t>
+          <t>12.15 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[29, 24, 22, 29, 24]</t>
+          <t>[8, 20, 16, 31, 16]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>53.44821975927021</v>
+        <v>62.56780601186749</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.27 segundos</t>
+          <t>11.33 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[29, 18, 9, 29, 9]</t>
+          <t>[16, 9, 9, 16, 22]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53.14601344522401</v>
+        <v>60.18903923077757</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.12 segundos</t>
+          <t>51.14 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[29, 22, 9, 29, 9]</t>
+          <t>[16, 9, 9, 16, 22]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>51.89529155470436</v>
+        <v>60.18903923077757</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.58 segundos</t>
+          <t>40.21 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[29, 22, 9, 29, 22]</t>
+          <t>[16, 9, 9, 16, 22]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.63540522778673</v>
+        <v>60.18903923077757</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30.80 segundos</t>
+          <t>44.33 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[7, 18, 27, 7, 23]</t>
+          <t>[11, 22, 5, 5, 17]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59.62212660921342</v>
+        <v>53.63218834744388</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.52 segundos</t>
+          <t>39.61 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[31, 25, 19, 19, 19]</t>
+          <t>[13, 25, 13, 5, 19]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>51.45596607127261</v>
+        <v>52.73465032444208</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.05 segundos</t>
+          <t>12.89 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[31, 25, 19, 19, 19]</t>
+          <t>[13, 25, 13, 5, 30]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.45596607127261</v>
+        <v>52.4573094373051</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.77 segundos</t>
+          <t>12.93 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[18, 10, 26, 18, 6]</t>
+          <t>[8, 18, 8, 18, 24]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>60.66022758319458</v>
+        <v>69.48255100859281</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>40.56 segundos</t>
+          <t>11.59 segundos</t>
         </is>
       </c>
     </row>
@@ -608,18 +608,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[18, 10, 26, 18, 6]</t>
+          <t>[8, 18, 8, 18, 24]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>60.66022758319458</v>
+        <v>69.48255100859281</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36.92 segundos</t>
+          <t>11.82 segundos</t>
         </is>
       </c>
     </row>
@@ -629,81 +629,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[18, 29, 12, 18, 6]</t>
+          <t>[8, 18, 8, 18, 24]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>59.93827917870134</v>
+        <v>69.48255100859281</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.85 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[3, 5, 3, 13, 5]</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>55.89124579129987</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>29.08 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>[3, 5, 3, 13, 5]</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>55.89124579129987</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>36.04 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>[3, 5, 3, 13, 5]</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>55.89124579129987</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>31.52 segundos</t>
+          <t>11.44 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[16, 9, 9, 16, 22]</t>
+          <t>[0, 12, 12, 0, 4]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>60.18903923077757</v>
+        <v>67.26025685397531</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>51.14 segundos</t>
+          <t>20.28 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[16, 9, 9, 16, 22]</t>
+          <t>[19, 14, 4, 4, 25]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60.18903923077757</v>
+        <v>54.43103937616288</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.21 segundos</t>
+          <t>12.22 segundos</t>
         </is>
       </c>
     </row>
@@ -503,144 +503,2055 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[16, 9, 9, 16, 22]</t>
+          <t>[19, 14, 4, 4, 25]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60.18903923077757</v>
+        <v>54.43103937616288</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44.33 segundos</t>
+          <t>12.20 segundos</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[11, 22, 5, 5, 17]</t>
+          <t>[12, 30, 12, 4, 25]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53.63218834744388</v>
+        <v>52.4573094373051</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39.61 segundos</t>
+          <t>11.31 segundos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[13, 25, 13, 5, 19]</t>
+          <t>[12, 30, 12, 4, 25]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52.73465032444208</v>
+        <v>52.4573094373051</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.89 segundos</t>
+          <t>11.12 segundos</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[13, 25, 13, 5, 30]</t>
+          <t>[12, 30, 12, 4, 25]</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>52.4573094373051</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.93 segundos</t>
+          <t>10.39 segundos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[8, 18, 8, 18, 24]</t>
+          <t>[12, 30, 12, 4, 25]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>69.48255100859281</v>
+        <v>52.4573094373051</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.59 segundos</t>
+          <t>9.90 segundos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[8, 18, 8, 18, 24]</t>
+          <t>[2, 28, 13, 2, 9]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>69.48255100859281</v>
+        <v>51.08384029266164</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.82 segundos</t>
+          <t>10.02 segundos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[2, 28, 13, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>51.08384029266164</v>
+      </c>
+      <c r="D10" t="n">
+        <v>38</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11.23 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[2, 28, 13, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>51.08384029266164</v>
+      </c>
+      <c r="D11" t="n">
+        <v>38</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>11.24 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[2, 28, 13, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>51.08384029266164</v>
+      </c>
+      <c r="D12" t="n">
+        <v>38</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>11.10 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[2, 28, 13, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>51.08384029266164</v>
+      </c>
+      <c r="D13" t="n">
+        <v>38</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10.96 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[2, 28, 13, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>51.08384029266164</v>
+      </c>
+      <c r="D14" t="n">
+        <v>38</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10.72 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[2, 28, 13, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>51.08384029266164</v>
+      </c>
+      <c r="D15" t="n">
+        <v>38</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10.16 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[2, 28, 13, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>51.08384029266164</v>
+      </c>
+      <c r="D16" t="n">
+        <v>38</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>11.40 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[2, 28, 13, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>51.08384029266164</v>
+      </c>
+      <c r="D17" t="n">
+        <v>38</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>9.53 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[2, 28, 22, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D18" t="n">
+        <v>82</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9.71 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>[2, 28, 22, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D19" t="n">
+        <v>82</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>11.50 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[2, 28, 22, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D20" t="n">
+        <v>82</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>11.09 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[2, 28, 22, 2, 9]</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D21" t="n">
+        <v>82</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>9.18 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>[28, 12, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>74.66264804761595</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>9.46 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>[14, 12, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>59.61402683401005</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10.31 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>3</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[8, 18, 8, 18, 24]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>69.48255100859281</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>[14, 12, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>59.61402683401005</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10.66 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[14, 12, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>59.61402683401005</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>10.59 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D26" t="n">
+        <v>23</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>10.18 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D27" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>8.20 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D28" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>11.53 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D29" t="n">
+        <v>23</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>9.39 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D30" t="n">
+        <v>23</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10.72 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D31" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10.87 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D32" t="n">
+        <v>23</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>10.58 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D33" t="n">
+        <v>23</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10.94 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>13</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D34" t="n">
+        <v>23</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>11.77 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>14</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D35" t="n">
+        <v>23</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10.38 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>15</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D36" t="n">
+        <v>23</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>11.11 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>16</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D37" t="n">
+        <v>23</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>11.56 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>17</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D38" t="n">
+        <v>23</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>11.22 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>18</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D39" t="n">
+        <v>23</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10.82 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>19</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D40" t="n">
+        <v>23</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>9.67 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>20</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>[14, 9, 12, 14, 14]</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>50.92812194004208</v>
+      </c>
+      <c r="D41" t="n">
+        <v>23</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10.28 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>18.09 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>13.44 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>14.28 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>12.49 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>18.04 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>15.72 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>13.17 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>13.54 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>9</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>10.30 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>10</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>12.93 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>11</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>10.39 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>12</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>11.73 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>13</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>11.31 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>14</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>[3, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>50.63540522778668</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>11.18 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>15</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>[20, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D56" t="n">
+        <v>74</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>11.42 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>16</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>[20, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D57" t="n">
+        <v>74</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>10.91 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>17</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>[20, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D58" t="n">
+        <v>74</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>10.34 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>18</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>[20, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D59" t="n">
+        <v>74</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>12.67 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>19</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>[20, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D60" t="n">
+        <v>74</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>12.13 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>20</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>[20, 30, 20, 3, 9]</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D61" t="n">
+        <v>74</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>12.18 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>[22, 16, 22, 31, 2]</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>80.69018836203885</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>11.69 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>[22, 16, 22, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>58.44637869921478</v>
+      </c>
+      <c r="D63" t="n">
+        <v>6</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>17.55 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>[22, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>52.46965796523451</v>
+      </c>
+      <c r="D64" t="n">
+        <v>11</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>11.04 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>[22, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>52.46965796523451</v>
+      </c>
+      <c r="D65" t="n">
+        <v>11</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>11.68 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>[22, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>52.46965796523451</v>
+      </c>
+      <c r="D66" t="n">
+        <v>11</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>10.38 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>[22, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>52.46965796523451</v>
+      </c>
+      <c r="D67" t="n">
+        <v>11</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>12.86 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>[22, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>52.46965796523451</v>
+      </c>
+      <c r="D68" t="n">
+        <v>11</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>10.32 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>[22, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>52.46965796523451</v>
+      </c>
+      <c r="D69" t="n">
+        <v>11</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>10.89 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>[22, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>52.46965796523451</v>
+      </c>
+      <c r="D70" t="n">
+        <v>11</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>11.76 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>[22, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>52.46965796523451</v>
+      </c>
+      <c r="D71" t="n">
+        <v>11</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>11.57 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>11</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>[10, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>50.39757452767356</v>
+      </c>
+      <c r="D72" t="n">
+        <v>50</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>11.20 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>12</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>[10, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>50.39757452767356</v>
+      </c>
+      <c r="D73" t="n">
+        <v>50</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>12.50 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>13</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>[10, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>50.39757452767356</v>
+      </c>
+      <c r="D74" t="n">
+        <v>50</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>11.04 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>14</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>[10, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>50.39757452767356</v>
+      </c>
+      <c r="D75" t="n">
+        <v>50</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>11.75 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>15</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>[10, 16, 15, 15, 15]</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>50.39757452767356</v>
+      </c>
+      <c r="D76" t="n">
+        <v>50</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>11.55 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>16</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>[10, 16, 15, 15, 12]</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>50.39757452767331</v>
+      </c>
+      <c r="D77" t="n">
+        <v>77</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>11.29 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>17</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>[10, 16, 15, 15, 12]</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>50.39757452767331</v>
+      </c>
+      <c r="D78" t="n">
+        <v>77</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>11.93 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>18</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>[10, 16, 15, 10, 12]</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>50.13035312668881</v>
+      </c>
+      <c r="D79" t="n">
+        <v>89</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>12.19 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>19</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>[10, 16, 15, 10, 12]</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>50.13035312668881</v>
+      </c>
+      <c r="D80" t="n">
+        <v>89</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>9.67 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>20</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>[10, 16, 15, 10, 12]</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>50.13035312668881</v>
+      </c>
+      <c r="D81" t="n">
+        <v>89</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>12.18 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>[21, 31, 21, 30, 22]</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>66.48439347806716</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>19.90 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>[21, 28, 0, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>53.6321883474438</v>
+      </c>
+      <c r="D83" t="n">
+        <v>7</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>14.46 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>3</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D84" t="n">
+        <v>14</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>13.18 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D85" t="n">
+        <v>14</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>12.88 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>5</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D86" t="n">
+        <v>14</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>11.93 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>6</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D87" t="n">
+        <v>14</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>11.91 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>7</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D88" t="n">
+        <v>14</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>11.79 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>8</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D89" t="n">
+        <v>14</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>11.03 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>9</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D90" t="n">
+        <v>14</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>10.76 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>10</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D91" t="n">
+        <v>14</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>12.28 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>11</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D92" t="n">
+        <v>14</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>11.40 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>12</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D93" t="n">
+        <v>14</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>11.49 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>13</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D94" t="n">
+        <v>14</v>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>11.44 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>14</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 17]</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>51.65845840858604</v>
+      </c>
+      <c r="D95" t="n">
+        <v>14</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>12.68 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>15</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 6]</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D96" t="n">
+        <v>72</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>13.17 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>16</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 6]</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D97" t="n">
+        <v>72</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>11.09 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>17</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 6]</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D98" t="n">
+        <v>72</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>10.57 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>18</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 6]</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D99" t="n">
+        <v>72</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>10.69 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>19</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 6]</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D100" t="n">
+        <v>72</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>13.44 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>20</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>[21, 28, 21, 0, 6]</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>50.5757782594587</v>
+      </c>
+      <c r="D101" t="n">
+        <v>72</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>11.56 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[15, 23, 9, 15, 24]</t>
+          <t>[26, 27, 18, 26, 8]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.27105962965972</v>
+        <v>53.78406304530412</v>
       </c>
       <c r="D2" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>190.33 segundos</t>
+          <t>67.48 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[15, 21, 15, 15, 15]</t>
+          <t>[26, 8, 14, 26, 21]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37.45090577403779</v>
+        <v>50.63540522778671</v>
       </c>
       <c r="D3" t="n">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>181.08 segundos</t>
+          <t>53.56 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[15, 21, 15, 15, 15]</t>
+          <t>[26, 8, 14, 26, 21]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.45090577403779</v>
+        <v>50.63540522778671</v>
       </c>
       <c r="D4" t="n">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>166.77 segundos</t>
+          <t>51.58 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[15, 21, 15, 15, 15]</t>
+          <t>[26, 8, 14, 26, 21]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.45090577403779</v>
+        <v>50.63540522778671</v>
       </c>
       <c r="D5" t="n">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>206.39 segundos</t>
+          <t>55.74 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,60 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[15, 21, 15, 15, 15]</t>
+          <t>[26, 8, 14, 26, 21]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.45090577403779</v>
+        <v>50.63540522778671</v>
       </c>
       <c r="D6" t="n">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>203.55 segundos</t>
+          <t>56.95 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[14, 8, 14, 26, 21]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50.57577825945872</v>
+      </c>
+      <c r="D7" t="n">
+        <v>135</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>55.12 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[14, 8, 14, 26, 21]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50.57577825945872</v>
+      </c>
+      <c r="D8" t="n">
+        <v>135</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>58.37 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[21, 3, 8, 8, 4]</t>
+          <t>[14, 21, 8, 8, 16]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52.58551582291764</v>
+        <v>53.63218834744402</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>189.73 segundos</t>
+          <t>83.49 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[8, 4, 8, 8, 4]</t>
+          <t>[14, 28, 8, 8, 21]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41.96414865973949</v>
+        <v>53.63218834744379</v>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>196.13 segundos</t>
+          <t>73.77 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[8, 4, 8, 8, 4]</t>
+          <t>[14, 7, 14, 0, 21]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41.96414865973949</v>
+        <v>50.57577825945872</v>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>179.92 segundos</t>
+          <t>74.46 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[8, 4, 8, 8, 4]</t>
+          <t>[14, 7, 14, 26, 21]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41.96414865973949</v>
+        <v>50.57577825945872</v>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>175.12 segundos</t>
+          <t>70.78 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[8, 22, 8, 8, 8]</t>
+          <t>[14, 31, 14, 14, 21]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.16487455259949</v>
+        <v>49.13545004407987</v>
       </c>
       <c r="D6" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>158.96 segundos</t>
+          <t>70.94 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[8, 22, 8, 8, 8]</t>
+          <t>[14, 31, 14, 14, 21]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37.16487455259949</v>
+        <v>49.13545004407987</v>
       </c>
       <c r="D7" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>155.07 segundos</t>
+          <t>77.73 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[8, 22, 8, 8, 8]</t>
+          <t>[14, 31, 14, 14, 21]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37.16487455259949</v>
+        <v>49.13545004407987</v>
       </c>
       <c r="D8" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>153.73 segundos</t>
+          <t>70.55 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[14, 21, 8, 8, 16]</t>
+          <t>[30, 25, 0, 0, 31]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53.63218834744402</v>
+        <v>65.83521779602701</v>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>83.49 segundos</t>
+          <t>194.17 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[14, 28, 8, 8, 21]</t>
+          <t>[30, 25, 0, 30, 25]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53.63218834744379</v>
+        <v>54.64114968988747</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>73.77 segundos</t>
+          <t>181.62 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[14, 7, 14, 0, 21]</t>
+          <t>[30, 25, 23, 30, 25]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.57577825945872</v>
+        <v>54.34710415922815</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.46 segundos</t>
+          <t>165.72 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[14, 7, 14, 26, 21]</t>
+          <t>[30, 25, 25, 30, 25]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.57577825945872</v>
+        <v>50.61144320511495</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70.78 segundos</t>
+          <t>134.85 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[14, 31, 14, 14, 21]</t>
+          <t>[30, 25, 25, 30, 30]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49.13545004407987</v>
+        <v>49.53884027612634</v>
       </c>
       <c r="D6" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>70.94 segundos</t>
+          <t>183.10 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[14, 31, 14, 14, 21]</t>
+          <t>[30, 25, 25, 30, 30]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.13545004407987</v>
+        <v>49.53884027612634</v>
       </c>
       <c r="D7" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.73 segundos</t>
+          <t>194.40 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,291 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[14, 31, 14, 14, 21]</t>
+          <t>[30, 21, 30, 30, 30]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>49.13545004407987</v>
+        <v>37.35722978728691</v>
       </c>
       <c r="D8" t="n">
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70.55 segundos</t>
+          <t>192.29 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D9" t="n">
+        <v>261</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>147.84 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D10" t="n">
+        <v>261</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>141.28 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D11" t="n">
+        <v>261</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>134.80 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D12" t="n">
+        <v>261</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>143.03 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D13" t="n">
+        <v>261</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>135.95 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D14" t="n">
+        <v>261</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>134.61 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D15" t="n">
+        <v>261</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>127.61 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D16" t="n">
+        <v>261</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>127.84 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D17" t="n">
+        <v>261</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>134.97 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D18" t="n">
+        <v>261</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>126.70 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D19" t="n">
+        <v>261</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>133.22 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D20" t="n">
+        <v>261</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>131.88 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[30, 21, 30, 30, 30]</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>37.35722978728691</v>
+      </c>
+      <c r="D21" t="n">
+        <v>261</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>134.73 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[30, 25, 0, 0, 31]</t>
+          <t>[3, 3, 13, 29, 9]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>65.83521779602701</v>
+        <v>63.21030899695463</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>194.17 segundos</t>
+          <t>57.88 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[30, 25, 0, 30, 25]</t>
+          <t>[16, 29, 2, 16, 9]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54.64114968988747</v>
+        <v>60.66022758319484</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>181.62 segundos</t>
+          <t>43.25 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[30, 25, 23, 30, 25]</t>
+          <t>[22, 29, 2, 2, 9]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>54.34710415922815</v>
+        <v>52.51270044950008</v>
       </c>
       <c r="D4" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>165.72 segundos</t>
+          <t>44.07 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[30, 25, 25, 30, 25]</t>
+          <t>[14, 29, 14, 2, 9]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.61144320511495</v>
+        <v>51.0242133243335</v>
       </c>
       <c r="D5" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>134.85 segundos</t>
+          <t>36.83 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[30, 25, 25, 30, 30]</t>
+          <t>[14, 8, 14, 2, 9]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49.53884027612634</v>
+        <v>50.92435253976508</v>
       </c>
       <c r="D6" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>183.10 segundos</t>
+          <t>40.15 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[30, 25, 25, 30, 30]</t>
+          <t>[14, 8, 14, 2, 23]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.53884027612634</v>
+        <v>50.57577825945869</v>
       </c>
       <c r="D7" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>194.40 segundos</t>
+          <t>44.98 segundos</t>
         </is>
       </c>
     </row>
@@ -587,291 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[30, 21, 30, 30, 30]</t>
+          <t>[14, 8, 14, 2, 23]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37.35722978728691</v>
+        <v>50.57577825945869</v>
       </c>
       <c r="D8" t="n">
-        <v>261</v>
+        <v>201</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>192.29 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D9" t="n">
-        <v>261</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>147.84 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D10" t="n">
-        <v>261</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>141.28 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D11" t="n">
-        <v>261</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>134.80 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D12" t="n">
-        <v>261</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>143.03 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D13" t="n">
-        <v>261</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>135.95 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D14" t="n">
-        <v>261</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>134.61 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D15" t="n">
-        <v>261</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>127.61 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D16" t="n">
-        <v>261</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>127.84 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D17" t="n">
-        <v>261</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>134.97 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D18" t="n">
-        <v>261</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>126.70 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D19" t="n">
-        <v>261</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>133.22 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D20" t="n">
-        <v>261</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>131.88 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>[30, 21, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>37.35722978728691</v>
-      </c>
-      <c r="D21" t="n">
-        <v>261</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>134.73 segundos</t>
+          <t>45.03 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[3, 3, 13, 29, 9]</t>
+          <t>[2, 17, 16, 31, 2]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>63.21030899695463</v>
+        <v>72.84192171434411</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>57.88 segundos</t>
+          <t>178.34 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[16, 29, 2, 16, 9]</t>
+          <t>[22, 28, 3, 22, 5]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60.66022758319484</v>
+        <v>54.10839558748251</v>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>43.25 segundos</t>
+          <t>187.87 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[22, 29, 2, 2, 9]</t>
+          <t>[22, 28, 3, 22, 28]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>52.51270044950008</v>
+        <v>52.78961316824333</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44.07 segundos</t>
+          <t>169.62 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[14, 29, 14, 2, 9]</t>
+          <t>[22, 28, 22, 22, 28]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>51.0242133243335</v>
+        <v>38.32974910519895</v>
       </c>
       <c r="D5" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.83 segundos</t>
+          <t>164.19 segundos</t>
         </is>
       </c>
     </row>
@@ -545,60 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[14, 8, 14, 2, 9]</t>
+          <t>[22, 28, 22, 22, 28]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50.92435253976508</v>
+        <v>38.32974910519895</v>
       </c>
       <c r="D6" t="n">
-        <v>194</v>
+        <v>145</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.15 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[14, 8, 14, 2, 23]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>50.57577825945869</v>
-      </c>
-      <c r="D7" t="n">
-        <v>201</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>44.98 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[14, 8, 14, 2, 23]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50.57577825945869</v>
-      </c>
-      <c r="D8" t="n">
-        <v>201</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>45.03 segundos</t>
+          <t>167.28 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[2, 17, 16, 31, 2]</t>
+          <t>[21, 13, 21, 31, 14]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>72.84192171434411</v>
+        <v>50.57577825945877</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>178.34 segundos</t>
+          <t>205.76 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[22, 28, 3, 22, 5]</t>
+          <t>[21, 8, 21, 31, 14]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54.10839558748251</v>
+        <v>50.57577825945873</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>187.87 segundos</t>
+          <t>228.98 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[22, 28, 3, 22, 28]</t>
+          <t>[21, 8, 21, 2, 14]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>52.78961316824333</v>
+        <v>50.57577825945872</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>169.62 segundos</t>
+          <t>238.80 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[22, 28, 22, 22, 28]</t>
+          <t>[21, 8, 21, 2, 14]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.32974910519895</v>
+        <v>50.57577825945872</v>
       </c>
       <c r="D5" t="n">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>164.19 segundos</t>
+          <t>267.61 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[22, 28, 22, 22, 28]</t>
+          <t>[21, 27, 21, 21, 14]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38.32974910519895</v>
+        <v>49.13545004407987</v>
       </c>
       <c r="D6" t="n">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>167.28 segundos</t>
+          <t>280.44 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[21, 13, 21, 31, 14]</t>
+          <t>[5, 0, 11, 5, 30]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50.57577825945877</v>
+        <v>52.71767037748877</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>205.76 segundos</t>
+          <t>324.39 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[21, 8, 21, 31, 14]</t>
+          <t>[5, 0, 11, 5, 23]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.57577825945873</v>
+        <v>51.9188193487697</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>228.98 segundos</t>
+          <t>391.33 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[21, 8, 21, 2, 14]</t>
+          <t>[5, 0, 5, 5, 23]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.57577825945872</v>
+        <v>49.13545004407987</v>
       </c>
       <c r="D4" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>238.80 segundos</t>
+          <t>349.04 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[21, 8, 21, 2, 14]</t>
+          <t>[5, 0, 5, 5, 14]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.57577825945872</v>
+        <v>41.61301147209003</v>
       </c>
       <c r="D5" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>267.61 segundos</t>
+          <t>246.82 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,60 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[21, 27, 21, 21, 14]</t>
+          <t>[5, 0, 5, 5, 14]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49.13545004407987</v>
+        <v>41.61301147209003</v>
       </c>
       <c r="D6" t="n">
-        <v>187</v>
+        <v>123</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>280.44 segundos</t>
+          <t>235.97 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[5, 0, 5, 5, 14]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>41.61301147209003</v>
+      </c>
+      <c r="D7" t="n">
+        <v>123</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>209.95 segundos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[5, 0, 5, 5, 14]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>41.61301147209003</v>
+      </c>
+      <c r="D8" t="n">
+        <v>123</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>234.65 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[31, 8, 31, 31, 25]</t>
+          <t>[24, 30, 14, 24, 6]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41.28932199160774</v>
+        <v>51.08384029266164</v>
       </c>
       <c r="D2" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>109.93 segundos</t>
+          <t>62.95 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[31, 8, 31, 31, 19]</t>
+          <t>[24, 30, 14, 24, 6]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.49047096288864</v>
+        <v>51.08384029266164</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>112.88 segundos</t>
+          <t>53.82 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[31, 26, 31, 31, 19]</t>
+          <t>[24, 18, 18, 24, 18]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.49047096288861</v>
+        <v>50.63540522778678</v>
       </c>
       <c r="D4" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>109.50 segundos</t>
+          <t>56.75 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[31, 26, 31, 31, 19]</t>
+          <t>[24, 18, 18, 24, 18]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.49047096288861</v>
+        <v>50.63540522778678</v>
       </c>
       <c r="D5" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>103.93 segundos</t>
+          <t>78.24 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[31, 26, 31, 31, 19]</t>
+          <t>[24, 18, 18, 24, 18]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.49047096288861</v>
+        <v>50.63540522778678</v>
       </c>
       <c r="D6" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>115.98 segundos</t>
+          <t>75.18 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[31, 26, 31, 31, 19]</t>
+          <t>[24, 18, 18, 24, 18]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40.49047096288861</v>
+        <v>50.63540522778678</v>
       </c>
       <c r="D7" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>118.59 segundos</t>
+          <t>76.57 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[31, 26, 31, 31, 19]</t>
+          <t>[24, 17, 18, 24, 18]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40.49047096288861</v>
+        <v>50.63540522778673</v>
       </c>
       <c r="D8" t="n">
-        <v>108</v>
+        <v>244</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>125.12 segundos</t>
+          <t>73.33 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[24, 30, 14, 24, 6]</t>
+          <t>[9, 23, 9, 9, 24]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>51.08384029266164</v>
+        <v>49.59999708396501</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>62.95 segundos</t>
+          <t>53.93 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[24, 30, 14, 24, 6]</t>
+          <t>[23, 5, 23, 30, 17]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>51.08384029266164</v>
+        <v>50.57577825945873</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53.82 segundos</t>
+          <t>53.02 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[24, 18, 18, 24, 18]</t>
+          <t>[27, 7, 13, 27, 23]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.63540522778678</v>
+        <v>50.63540522778671</v>
       </c>
       <c r="D4" t="n">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>56.75 segundos</t>
+          <t>52.89 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[24, 18, 18, 24, 18]</t>
+          <t>[27, 6, 1, 13, 12]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.63540522778678</v>
+        <v>72.13305233995774</v>
       </c>
       <c r="D5" t="n">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>78.24 segundos</t>
+          <t>48.51 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[24, 18, 18, 24, 18]</t>
+          <t>[12, 14, 27, 21, 3]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50.63540522778678</v>
+        <v>72.11586798580535</v>
       </c>
       <c r="D6" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75.18 segundos</t>
+          <t>51.56 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[24, 18, 18, 24, 18]</t>
+          <t>[10, 1, 18, 10, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50.63540522778678</v>
+        <v>52.38336638865479</v>
       </c>
       <c r="D7" t="n">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.57 segundos</t>
+          <t>51.87 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[24, 17, 18, 24, 18]</t>
+          <t>[21, 0, 14, 8, 25]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50.63540522778673</v>
+        <v>77.80827966252565</v>
       </c>
       <c r="D8" t="n">
-        <v>244</v>
+        <v>22</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73.33 segundos</t>
+          <t>49.20 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[9, 23, 9, 9, 24]</t>
+          <t>[30, 26, 26, 15, 26]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>49.59999708396501</v>
+        <v>68.36566647576245</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.93 segundos</t>
+          <t>58.82 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[23, 5, 23, 30, 17]</t>
+          <t>[18, 26, 30, 30, 26]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.57577825945873</v>
+        <v>51.90766739450599</v>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53.02 segundos</t>
+          <t>54.67 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[27, 7, 13, 27, 23]</t>
+          <t>[18, 26, 30, 30, 26]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.63540522778671</v>
+        <v>51.90766739450599</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.89 segundos</t>
+          <t>53.59 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[27, 6, 1, 13, 12]</t>
+          <t>[30, 12, 30, 30, 12]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72.13305233995774</v>
+        <v>38.32974910519897</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>48.51 segundos</t>
+          <t>52.65 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[12, 14, 27, 21, 3]</t>
+          <t>[30, 12, 30, 30, 13]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.11586798580535</v>
+        <v>38.2524339321469</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>189</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>51.56 segundos</t>
+          <t>55.67 segundos</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[10, 1, 18, 10, 1]</t>
+          <t>[30, 12, 30, 30, 30]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>52.38336638865479</v>
+        <v>37.16487455259929</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>51.87 segundos</t>
+          <t>49.17 segundos</t>
         </is>
       </c>
     </row>
@@ -587,18 +587,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[21, 0, 14, 8, 25]</t>
+          <t>[30, 12, 30, 30, 30]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>77.80827966252565</v>
+        <v>37.16487455259929</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>207</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>49.20 segundos</t>
+          <t>51.03 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[30, 26, 26, 15, 26]</t>
+          <t>[1, 23, 22, 28, 11]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>68.36566647576245</v>
+        <v>62.76187393207982</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>58.82 segundos</t>
+          <t>59.24 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[18, 26, 30, 30, 26]</t>
+          <t>[28, 4, 22, 28, 11]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>51.90766739450599</v>
+        <v>50.63540522778671</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54.67 segundos</t>
+          <t>54.20 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[18, 26, 30, 30, 26]</t>
+          <t>[28, 4, 22, 28, 11]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>51.90766739450599</v>
+        <v>50.63540522778671</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.59 segundos</t>
+          <t>51.24 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[30, 12, 30, 30, 12]</t>
+          <t>[28, 4, 22, 28, 11]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.32974910519897</v>
+        <v>50.63540522778671</v>
       </c>
       <c r="D5" t="n">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>52.65 segundos</t>
+          <t>53.52 segundos</t>
         </is>
       </c>
     </row>
@@ -545,60 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[30, 12, 30, 30, 13]</t>
+          <t>[28, 4, 22, 28, 11]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38.2524339321469</v>
+        <v>50.63540522778671</v>
       </c>
       <c r="D6" t="n">
-        <v>189</v>
+        <v>47</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.67 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>[30, 12, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>37.16487455259929</v>
-      </c>
-      <c r="D7" t="n">
-        <v>207</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>49.17 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[30, 12, 30, 30, 30]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>37.16487455259929</v>
-      </c>
-      <c r="D8" t="n">
-        <v>207</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>51.03 segundos</t>
+          <t>51.46 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 23, 22, 28, 11]</t>
+          <t>[22, 4, 13, 13, 23]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>62.76187393207982</v>
+        <v>62.99119480529274</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>59.24 segundos</t>
+          <t>54.93 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[28, 4, 22, 28, 11]</t>
+          <t>[23, 3, 2, 2, 23]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.63540522778671</v>
+        <v>51.15077448618497</v>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54.20 segundos</t>
+          <t>54.90 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[28, 4, 22, 28, 11]</t>
+          <t>[23, 3, 2, 2, 23]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.63540522778671</v>
+        <v>51.15077448618497</v>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.24 segundos</t>
+          <t>53.81 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[28, 4, 22, 28, 11]</t>
+          <t>[23, 3, 2, 2, 25]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.63540522778671</v>
+        <v>50.74090747764224</v>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>53.52 segundos</t>
+          <t>51.17 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[28, 4, 22, 28, 11]</t>
+          <t>[23, 2, 2, 2, 25]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50.63540522778671</v>
+        <v>50.11678075686478</v>
       </c>
       <c r="D6" t="n">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>51.46 segundos</t>
+          <t>52.25 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[22, 4, 13, 13, 23]</t>
+          <t>[3, 30, 9, 3, 21]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>62.99119480529274</v>
+        <v>50.63540522778668</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>54.93 segundos</t>
+          <t>71.38 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[23, 3, 2, 2, 23]</t>
+          <t>[9, 16, 9, 9, 21]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>51.15077448618497</v>
+        <v>41.6130114720901</v>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54.90 segundos</t>
+          <t>66.82 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[23, 3, 2, 2, 23]</t>
+          <t>[9, 0, 9, 9, 17]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>51.15077448618497</v>
+        <v>41.61301147209003</v>
       </c>
       <c r="D4" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.81 segundos</t>
+          <t>66.62 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[23, 3, 2, 2, 25]</t>
+          <t>[9, 0, 9, 9, 17]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.74090747764224</v>
+        <v>41.61301147209003</v>
       </c>
       <c r="D5" t="n">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>51.17 segundos</t>
+          <t>63.01 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[23, 2, 2, 2, 25]</t>
+          <t>[9, 0, 9, 9, 17]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50.11678075686478</v>
+        <v>41.61301147209003</v>
       </c>
       <c r="D6" t="n">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>52.25 segundos</t>
+          <t>62.19 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[3, 30, 9, 3, 21]</t>
+          <t>[29, 14, 29, 29, 15]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50.63540522778668</v>
+        <v>38.834191826204</v>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>71.38 segundos</t>
+          <t>65.80 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[9, 16, 9, 9, 21]</t>
+          <t>[29, 14, 29, 29, 29]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41.6130114720901</v>
+        <v>37.41644688181734</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66.82 segundos</t>
+          <t>64.08 segundos</t>
         </is>
       </c>
     </row>
@@ -503,18 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 17]</t>
+          <t>[29, 14, 29, 29, 29]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41.61301147209003</v>
+        <v>37.41644688181734</v>
       </c>
       <c r="D4" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66.62 segundos</t>
+          <t>64.15 segundos</t>
         </is>
       </c>
     </row>
@@ -524,18 +524,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 17]</t>
+          <t>[29, 14, 29, 29, 29]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41.61301147209003</v>
+        <v>37.41644688181734</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>63.01 segundos</t>
+          <t>62.67 segundos</t>
         </is>
       </c>
     </row>
@@ -545,18 +545,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 9, 17]</t>
+          <t>[29, 14, 29, 29, 29]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41.61301147209003</v>
+        <v>37.41644688181734</v>
       </c>
       <c r="D6" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>62.19 segundos</t>
+          <t>61.69 segundos</t>
         </is>
       </c>
     </row>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -1,37 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Config 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>execution</t>
+  </si>
+  <si>
+    <t>solution_variables</t>
+  </si>
+  <si>
+    <t>best_fitness</t>
+  </si>
+  <si>
+    <t>best_generations</t>
+  </si>
+  <si>
+    <t>execution_time</t>
+  </si>
+  <si>
+    <t>[31, 0, 31, 31, 14]</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +72,36 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,147 +389,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>execution</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>solution_variables</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>best_fitness</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>best_generations</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>execution_time</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[29, 14, 29, 29, 15]</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>38.834191826204</v>
-      </c>
-      <c r="D2" t="n">
-        <v>29</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>65.80 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[29, 14, 29, 29, 29]</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>37.41644688181734</v>
-      </c>
-      <c r="D3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>64.08 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[29, 14, 29, 29, 29]</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>37.41644688181734</v>
-      </c>
-      <c r="D4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>64.15 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[29, 14, 29, 29, 29]</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>37.41644688181734</v>
-      </c>
-      <c r="D5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>62.67 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[29, 14, 29, 29, 29]</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>37.41644688181734</v>
-      </c>
-      <c r="D6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>61.69 segundos</t>
-        </is>
+      <c r="C2">
+        <v>47.22428477519509</v>
+      </c>
+      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.0002879623263888889</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -7,14 +7,17 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Config 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Consolidated Results" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>config_num</t>
+  </si>
   <si>
     <t>execution</t>
   </si>
@@ -31,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[31, 0, 31, 31, 14]</t>
+    <t>[1, 15, 1, 31, 23]</t>
   </si>
 </sst>
 </file>
@@ -90,12 +93,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -390,10 +392,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -409,22 +411,28 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>51.6519701753148</v>
+      </c>
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>47.22428477519509</v>
-      </c>
-      <c r="D2">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.0002879623263888889</v>
+      <c r="F2">
+        <v>31.130852</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[1, 15, 1, 31, 23]</t>
+    <t>[29, 2, 29, 11, 3]</t>
   </si>
 </sst>
 </file>
@@ -426,13 +426,13 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>51.6519701753148</v>
+        <v>53.58329360731427</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>31.130852</v>
+        <v>26.58761</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[29, 2, 29, 11, 3]</t>
+    <t>[17, 29, 17, 24, 3]</t>
   </si>
 </sst>
 </file>
@@ -417,7 +417,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -426,13 +426,13 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>53.58329360731427</v>
+        <v>73.5043558341541</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>26.58761</v>
+        <v>25.409876</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[17, 29, 17, 24, 3]</t>
+    <t>[9, 2, 17, 17, 11]</t>
   </si>
 </sst>
 </file>
@@ -417,22 +417,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>73.5043558341541</v>
+        <v>50.79011875802</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>25.409876</v>
+        <v>64.700166</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[9, 2, 17, 17, 11]</t>
+    <t>[4, 20, 31, 31, 20]</t>
   </si>
 </sst>
 </file>
@@ -417,7 +417,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -426,13 +426,13 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>50.79011875802</v>
+        <v>51.64503337748438</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>64.700166</v>
+        <v>64.124133</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[4, 20, 31, 31, 20]</t>
+    <t>[17, 3, 17, 17, 19]</t>
   </si>
 </sst>
 </file>
@@ -417,22 +417,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>51.64503337748438</v>
+        <v>37.43609562399138</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F2">
-        <v>64.124133</v>
+        <v>1306.416416</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[17, 3, 17, 17, 19]</t>
+    <t>[9, 4, 9, 9, 19]</t>
   </si>
 </sst>
 </file>
@@ -426,13 +426,13 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>37.43609562399138</v>
+        <v>41.61301147209003</v>
       </c>
       <c r="E2">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>1306.416416</v>
+        <v>790.98672</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[9, 4, 9, 9, 19]</t>
+    <t>[29, 22, 29, 29, 29]</t>
   </si>
 </sst>
 </file>
@@ -426,13 +426,13 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>41.61301147209003</v>
+        <v>37.9671225552687</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>790.98672</v>
+        <v>767.71467</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[29, 22, 29, 29, 29]</t>
+    <t>[21, 2, 21, 21, 7]</t>
   </si>
 </sst>
 </file>
@@ -426,13 +426,13 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>37.9671225552687</v>
+        <v>49.13545004407987</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>767.71467</v>
+        <v>811.3702</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[21, 2, 21, 21, 7]</t>
+    <t>[14, 20, 14, 14, 14]</t>
   </si>
 </sst>
 </file>
@@ -426,13 +426,13 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>49.13545004407987</v>
+        <v>37.87772291416114</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>811.3702</v>
+        <v>802.644562</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>[3, 2, 3, 29, 3]</t>
+    <t>[21, 8, 21, 21, 16]</t>
   </si>
 </sst>
 </file>
@@ -426,13 +426,13 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>51.04032529934373</v>
+        <v>48.80058064405528</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>90.98234600000001</v>
+        <v>81.234189</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -16,25 +16,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
+    <t>execution</t>
+  </si>
+  <si>
+    <t>solution_variables</t>
+  </si>
+  <si>
+    <t>best_fitness</t>
+  </si>
+  <si>
+    <t>best_generations</t>
+  </si>
+  <si>
+    <t>execution_time</t>
+  </si>
+  <si>
     <t>config_num</t>
   </si>
   <si>
-    <t>execution</t>
-  </si>
-  <si>
-    <t>solution_variables</t>
-  </si>
-  <si>
-    <t>best_fitness</t>
-  </si>
-  <si>
-    <t>best_generations</t>
-  </si>
-  <si>
-    <t>execution_time</t>
-  </si>
-  <si>
-    <t>[21, 8, 21, 21, 16]</t>
+    <t>[2, 9, 23, 2, 15]</t>
   </si>
 </sst>
 </file>
@@ -419,20 +419,20 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>50.63540522778671</v>
+      </c>
+      <c r="D2">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>91.50167999999999</v>
+      </c>
+      <c r="F2">
         <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>48.80058064405528</v>
-      </c>
-      <c r="E2">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>81.234189</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -34,7 +34,7 @@
     <t>config_num</t>
   </si>
   <si>
-    <t>[2, 9, 23, 2, 15]</t>
+    <t>[30, 19, 30, 30, 30]</t>
   </si>
 </sst>
 </file>
@@ -423,13 +423,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>50.63540522778671</v>
+        <v>37.16487455259924</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E2">
-        <v>91.50167999999999</v>
+        <v>373.857207</v>
       </c>
       <c r="F2">
         <v>1</v>

--- a/src/output/results_consolidados.xlsx
+++ b/src/output/results_consolidados.xlsx
@@ -16,6 +16,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
+    <t>config_num</t>
+  </si>
+  <si>
     <t>execution</t>
   </si>
   <si>
@@ -31,10 +34,7 @@
     <t>execution_time</t>
   </si>
   <si>
-    <t>config_num</t>
-  </si>
-  <si>
-    <t>[30, 19, 30, 30, 30]</t>
+    <t>[8, 9, 22, 22, 8]</t>
   </si>
 </sst>
 </file>
@@ -419,20 +419,20 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>37.16487455259924</v>
-      </c>
       <c r="D2">
-        <v>41</v>
+        <v>50.62849554405395</v>
       </c>
       <c r="E2">
-        <v>373.857207</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>127.346984</v>
       </c>
     </row>
   </sheetData>
